--- a/Docs/WBS_IFEA.xlsx
+++ b/Docs/WBS_IFEA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Codelab\Desktop\Unity\TeamProject_IFEA\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Codelab\Desktop\Unity\TeamProject_IFEA\TeamProject_IFEA\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F92C0DB-4536-413C-A6A5-D63F4D540686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E74EE67-BAEC-4600-997E-241FE101F248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="프로젝트WBS" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="155">
   <si>
     <t xml:space="preserve">실적기준일 : </t>
   </si>
@@ -921,7 +921,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="81">
+  <borders count="80">
     <border>
       <left/>
       <right/>
@@ -1525,19 +1525,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF666666"/>
       </left>
@@ -1947,7 +1934,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2056,12 +2043,6 @@
     <xf numFmtId="176" fontId="27" fillId="0" borderId="28" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="36" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="27" fillId="0" borderId="29" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2245,9 +2226,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="34" fillId="11" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2266,325 +2244,280 @@
     <xf numFmtId="0" fontId="34" fillId="12" borderId="39" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="28" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="32" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="34" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="22" fillId="15" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="41" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="36" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="42" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="43" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="47" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="48" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="49" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="11" borderId="50" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="11" borderId="50" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="11" borderId="50" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="55" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="54" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="54" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="54" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="11" borderId="62" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="11" borderId="63" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="11" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="12" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="58" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="60" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="71" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="72" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="70" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="73" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="74" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="72" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="65" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="75" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="76" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="77" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="79" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="78" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="12" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="12" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="38" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="11" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="8" borderId="14" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="28" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="28" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="32" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="32" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="34" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="34" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="38" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="15" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="41" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="36" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="42" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="43" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="47" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="48" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="49" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="50" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="51" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="11" borderId="52" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="11" borderId="52" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="52" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="54" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="54" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="56" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="56" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="56" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="59" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="60" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="63" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="64" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="65" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="30" fillId="12" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="59" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="61" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="61" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="62" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="71" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="72" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="73" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="72" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="74" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="75" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="66" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="67" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="70" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="73" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="66" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="67" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="66" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="67" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="70" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="76" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="77" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="78" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="79" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="80" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="79" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="30" fillId="12" borderId="12" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="30" fillId="12" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2874,60 +2807,59 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:AE1006"/>
+  <dimension ref="A1:AD1006"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="1.28515625" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="51" customWidth="1"/>
-    <col min="4" max="4" width="16" style="51" customWidth="1"/>
-    <col min="5" max="5" width="12" style="51" customWidth="1"/>
-    <col min="6" max="6" width="34" style="51" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" style="51" customWidth="1"/>
-    <col min="8" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="54.85546875" customWidth="1"/>
-    <col min="11" max="21" width="16.5703125" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" customWidth="1"/>
-    <col min="23" max="31" width="5" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="49" customWidth="1"/>
+    <col min="4" max="4" width="16" style="49" customWidth="1"/>
+    <col min="5" max="5" width="12" style="49" customWidth="1"/>
+    <col min="6" max="6" width="50.140625" style="49" customWidth="1"/>
+    <col min="7" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="54.85546875" customWidth="1"/>
+    <col min="10" max="20" width="16.5703125" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" customWidth="1"/>
+    <col min="22" max="30" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="35.25" customHeight="1">
+    <row r="1" spans="1:30" ht="35.25" customHeight="1">
       <c r="A1" s="11"/>
       <c r="B1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="14"/>
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="16">
+      <c r="J1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="16">
         <v>46302</v>
       </c>
+      <c r="L1" s="17"/>
       <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
+      <c r="N1" s="191"/>
+      <c r="O1" s="191"/>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" s="19">
-        <f>U5/S5</f>
-        <v>1.8499999999999999</v>
-      </c>
-      <c r="V1" s="20" t="str">
-        <f>IF(U1&lt;0.75,"(위험)",IF(U1&lt;0.85,"(경고)",IF(U1&lt;0.95,"(주의)","(양호)")))</f>
+      <c r="S1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="19">
+        <f>T5/R5</f>
+        <v>1.8</v>
+      </c>
+      <c r="U1" s="20" t="str">
+        <f>IF(T1&lt;0.75,"(위험)",IF(T1&lt;0.85,"(경고)",IF(T1&lt;0.95,"(주의)","(양호)")))</f>
         <v>(양호)</v>
       </c>
+      <c r="V1" s="21"/>
       <c r="W1" s="21"/>
       <c r="X1" s="21"/>
       <c r="Y1" s="21"/>
@@ -2936,31 +2868,30 @@
       <c r="AB1" s="21"/>
       <c r="AC1" s="21"/>
       <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
     </row>
-    <row r="2" spans="1:31" ht="6" customHeight="1">
+    <row r="2" spans="1:30" ht="6" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="22"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="24"/>
       <c r="N2" s="24"/>
       <c r="O2" s="24"/>
       <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="26"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="27"/>
       <c r="T2" s="27"/>
       <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
+      <c r="V2" s="21"/>
       <c r="W2" s="21"/>
       <c r="X2" s="21"/>
       <c r="Y2" s="21"/>
@@ -2969,233 +2900,231 @@
       <c r="AB2" s="21"/>
       <c r="AC2" s="21"/>
       <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
     </row>
-    <row r="3" spans="1:31" ht="21" customHeight="1">
+    <row r="3" spans="1:30" ht="21" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="110" t="s">
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="110"/>
-      <c r="H3" s="111" t="s">
+      <c r="G3" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="112" t="s">
+      <c r="H3" s="193"/>
+      <c r="I3" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="114" t="s">
+      <c r="J3" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="114" t="s">
+      <c r="K3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="114" t="s">
+      <c r="L3" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="114" t="s">
+      <c r="M3" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="114" t="s">
+      <c r="N3" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="114" t="s">
+      <c r="O3" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="114" t="s">
+      <c r="P3" s="195" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="116" t="s">
+      <c r="Q3" s="185" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="117" t="s">
+      <c r="R3" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="118" t="s">
+      <c r="S3" s="187" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="119" t="s">
+      <c r="T3" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="119"/>
-      <c r="W3" s="131" t="s">
+      <c r="U3" s="188"/>
+      <c r="V3" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="131"/>
-      <c r="Y3" s="131"/>
-      <c r="Z3" s="131"/>
-      <c r="AA3" s="131"/>
-      <c r="AB3" s="131"/>
-      <c r="AC3" s="131"/>
-      <c r="AD3" s="131"/>
-      <c r="AE3" s="131"/>
+      <c r="W3" s="183"/>
+      <c r="X3" s="183"/>
+      <c r="Y3" s="183"/>
+      <c r="Z3" s="183"/>
+      <c r="AA3" s="183"/>
+      <c r="AB3" s="183"/>
+      <c r="AC3" s="183"/>
+      <c r="AD3" s="183"/>
     </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1">
+    <row r="4" spans="1:30" ht="18.75" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="B4" s="192"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="113" t="s">
+      <c r="H4" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="52" t="s">
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+      <c r="L4" s="195"/>
+      <c r="M4" s="195"/>
+      <c r="N4" s="195"/>
+      <c r="O4" s="195"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="185"/>
+      <c r="R4" s="186"/>
+      <c r="S4" s="187"/>
+      <c r="T4" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="52" t="s">
+      <c r="U4" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="W4" s="132" t="s">
+      <c r="V4" s="184" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="132"/>
-      <c r="Y4" s="132"/>
-      <c r="Z4" s="132"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="132"/>
-      <c r="AC4" s="132"/>
-      <c r="AD4" s="132"/>
-      <c r="AE4" s="132"/>
+      <c r="W4" s="184"/>
+      <c r="X4" s="184"/>
+      <c r="Y4" s="184"/>
+      <c r="Z4" s="184"/>
+      <c r="AA4" s="184"/>
+      <c r="AB4" s="184"/>
+      <c r="AC4" s="184"/>
+      <c r="AD4" s="184"/>
     </row>
-    <row r="5" spans="1:31" ht="18" customHeight="1">
+    <row r="5" spans="1:30" ht="18" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="115"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="55">
-        <f>MIN(K6:K56)</f>
+      <c r="E5" s="196"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
+      <c r="J5" s="53">
+        <f>MIN(J6:J56)</f>
         <v>46301</v>
       </c>
-      <c r="L5" s="55">
-        <f>MAX(L6:L56)</f>
+      <c r="K5" s="53">
+        <f>MAX(K6:K56)</f>
         <v>46309</v>
       </c>
-      <c r="M5" s="55">
-        <f>MIN(M6:M56)</f>
+      <c r="L5" s="53">
+        <f>MIN(L6:L56)</f>
         <v>46301</v>
       </c>
-      <c r="N5" s="55">
-        <f>MAX(N6:N56)</f>
+      <c r="M5" s="53">
+        <f>MAX(M6:M56)</f>
         <v>46302</v>
       </c>
-      <c r="O5" s="56">
-        <f t="shared" ref="O5:T5" si="0">O57</f>
-        <v>37</v>
-      </c>
-      <c r="P5" s="56">
+      <c r="N5" s="54">
+        <f t="shared" ref="N5:R5" si="0">N57</f>
+        <v>42</v>
+      </c>
+      <c r="O5" s="54">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Q5" s="56">
+        <v>7</v>
+      </c>
+      <c r="P5" s="54">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="R5" s="56">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="54">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="S5" s="57">
+        <v>7</v>
+      </c>
+      <c r="R5" s="55">
         <f t="shared" si="0"/>
-        <v>8.1081081081081086E-2</v>
-      </c>
-      <c r="T5" s="57">
-        <f t="shared" si="0"/>
-        <v>8.1081081081081086E-2</v>
-      </c>
-      <c r="U5" s="58">
-        <f>(AVERAGE(U6:U8)*C6)+(AVERAGE(U12:U15)*C12)+(AVERAGE(U18:U31)*C18)+(AVERAGE(U47:U49)*C47)+(AVERAGE(U52:U54)*C52)</f>
-        <v>0.15</v>
-      </c>
-      <c r="V5" s="58">
-        <f t="shared" ref="V5:W57" si="1">U5-S5</f>
-        <v>6.8918918918918909E-2</v>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="S5" s="55">
+        <f>S57</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="T5" s="56">
+        <f>(AVERAGE(T6:T8)*C6)+(AVERAGE(T12:T15)*C12)+(AVERAGE(T18:T46)*C18)+(AVERAGE(T47:T50)*C47)+(AVERAGE(T52:T53)*C52)</f>
+        <v>0.3</v>
+      </c>
+      <c r="U5" s="56">
+        <f t="shared" ref="U5:U57" si="1">T5-R5</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V5" s="28">
+        <v>46301</v>
       </c>
       <c r="W5" s="28">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="X5" s="28">
-        <v>46302</v>
-      </c>
-      <c r="Y5" s="28">
         <v>46303</v>
       </c>
-      <c r="Z5" s="133">
+      <c r="Y5" s="110">
         <v>46304</v>
       </c>
-      <c r="AA5" s="133">
+      <c r="Z5" s="110">
         <v>46305</v>
       </c>
-      <c r="AB5" s="133">
+      <c r="AA5" s="110">
         <v>11</v>
       </c>
+      <c r="AB5" s="28">
+        <v>12</v>
+      </c>
       <c r="AC5" s="28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD5" s="28">
-        <v>13</v>
-      </c>
-      <c r="AE5" s="28">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="30" customHeight="1">
+    <row r="6" spans="1:30" ht="30" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="29">
         <v>1</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="57">
         <v>0.15</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="136" t="s">
+      <c r="E6" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="120" t="s">
+      <c r="F6" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="121"/>
-      <c r="H6" s="61" t="s">
+      <c r="G6" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="H6" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="63" t="s">
+      <c r="I6" s="61" t="s">
         <v>31</v>
+      </c>
+      <c r="J6" s="34">
+        <v>46301</v>
       </c>
       <c r="K6" s="34">
         <v>46301</v>
@@ -3206,73 +3135,72 @@
       <c r="M6" s="34">
         <v>46301</v>
       </c>
-      <c r="N6" s="34">
-        <v>46301</v>
-      </c>
-      <c r="O6" s="64">
-        <f t="shared" ref="O6:O56" si="2">IF(OR(K6="",L6=""),0,L6-K6+1)</f>
-        <v>1</v>
-      </c>
-      <c r="P6" s="65">
-        <f t="shared" ref="P6:P56" si="3">IF(OR(M6="",N6=""),0,N6-M6+1)</f>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="62">
-        <f t="shared" ref="Q6:Q56" si="4">IF(O6=0,0,MAX(0,MIN(O6,$L$1-K6+1)))</f>
-        <v>1</v>
-      </c>
-      <c r="R6" s="66">
-        <f t="shared" ref="R6:R56" si="5">IF(P6=0,0,MIN(P6,O6))</f>
-        <v>1</v>
-      </c>
-      <c r="S6" s="67">
-        <f t="shared" ref="S6:S57" si="6">IFERROR(Q6/O6,0)</f>
-        <v>1</v>
-      </c>
-      <c r="T6" s="68">
-        <f t="shared" ref="T6:T57" si="7">IFERROR(R6/O6,0)</f>
-        <v>1</v>
-      </c>
-      <c r="U6" s="69">
-        <f t="shared" ref="U6:U56" si="8">IF(OR(O6=0,R6=0),0,MIN(1,R6/O6))</f>
-        <v>1</v>
-      </c>
-      <c r="V6" s="177">
+      <c r="N6" s="62">
+        <f t="shared" ref="N6:N56" si="2">IF(OR(J6="",K6=""),0,K6-J6+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="63">
+        <f t="shared" ref="O6:O56" si="3">IF(OR(L6="",M6=""),0,M6-L6+1)</f>
+        <v>1</v>
+      </c>
+      <c r="P6" s="60">
+        <f>IF(N6=0,0,MAX(0,MIN(N6,$K$1-J6+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="64">
+        <f t="shared" ref="Q6:Q56" si="4">IF(O6=0,0,MIN(O6,N6))</f>
+        <v>1</v>
+      </c>
+      <c r="R6" s="65">
+        <f t="shared" ref="R6:R57" si="5">IFERROR(P6/N6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S6" s="66">
+        <f t="shared" ref="S6:S57" si="6">IFERROR(Q6/N6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T6" s="67">
+        <f t="shared" ref="T6:T56" si="7">IF(OR(N6=0,Q6=0),0,MIN(1,Q6/N6))</f>
+        <v>1</v>
+      </c>
+      <c r="U6" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W6" s="181" t="s">
+      <c r="V6" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="X6" s="153"/>
-      <c r="Y6" s="161"/>
-      <c r="Z6" s="169"/>
-      <c r="AA6" s="154"/>
-      <c r="AB6" s="170"/>
-      <c r="AC6" s="166"/>
-      <c r="AD6" s="154"/>
-      <c r="AE6" s="170"/>
+      <c r="W6" s="128"/>
+      <c r="X6" s="134"/>
+      <c r="Y6" s="142"/>
+      <c r="Z6" s="128"/>
+      <c r="AA6" s="143"/>
+      <c r="AB6" s="139"/>
+      <c r="AC6" s="128"/>
+      <c r="AD6" s="143"/>
     </row>
-    <row r="7" spans="1:31" ht="30" customHeight="1">
+    <row r="7" spans="1:30" ht="30" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="29"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="136" t="s">
+      <c r="C7" s="68"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="120" t="s">
+      <c r="F7" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="121"/>
-      <c r="H7" s="61" t="s">
+      <c r="G7" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="62" t="s">
+      <c r="H7" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="63" t="s">
+      <c r="I7" s="61" t="s">
         <v>35</v>
+      </c>
+      <c r="J7" s="34">
+        <v>46301</v>
       </c>
       <c r="K7" s="34">
         <v>46301</v>
@@ -3283,73 +3211,72 @@
       <c r="M7" s="34">
         <v>46301</v>
       </c>
-      <c r="N7" s="34">
-        <v>46301</v>
-      </c>
-      <c r="O7" s="64">
+      <c r="N7" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P7" s="65">
+      <c r="O7" s="63">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="P7" s="60">
+        <f>IF(N7=0,0,MAX(0,MIN(N7,$K$1-J7+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="64">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="65">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="66">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="67">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U7" s="69">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="V7" s="177">
+      <c r="U7" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W7" s="182" t="s">
+      <c r="V7" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="X7" s="155"/>
-      <c r="Y7" s="162"/>
-      <c r="Z7" s="171"/>
-      <c r="AA7" s="156"/>
-      <c r="AB7" s="172"/>
-      <c r="AC7" s="158"/>
-      <c r="AD7" s="156"/>
-      <c r="AE7" s="172"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="135"/>
+      <c r="Y7" s="144"/>
+      <c r="Z7" s="129"/>
+      <c r="AA7" s="145"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="145"/>
     </row>
-    <row r="8" spans="1:31" ht="30" customHeight="1">
+    <row r="8" spans="1:30" ht="30" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="136" t="s">
+      <c r="C8" s="68"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="120" t="s">
+      <c r="F8" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="121"/>
-      <c r="H8" s="61" t="s">
+      <c r="G8" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="62" t="s">
+      <c r="H8" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="63" t="s">
+      <c r="I8" s="61" t="s">
         <v>38</v>
+      </c>
+      <c r="J8" s="34">
+        <v>46301</v>
       </c>
       <c r="K8" s="34">
         <v>46301</v>
@@ -3360,248 +3287,244 @@
       <c r="M8" s="34">
         <v>46301</v>
       </c>
-      <c r="N8" s="34">
-        <v>46301</v>
-      </c>
-      <c r="O8" s="64">
+      <c r="N8" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P8" s="65">
+      <c r="O8" s="63">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="62">
+      <c r="P8" s="60">
+        <f>IF(N8=0,0,MAX(0,MIN(N8,$K$1-J8+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="64">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="R8" s="66">
+      <c r="R8" s="65">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="S8" s="67">
+      <c r="S8" s="66">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="T8" s="68">
+      <c r="T8" s="67">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="U8" s="69">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="V8" s="177">
+      <c r="U8" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W8" s="182" t="s">
+      <c r="V8" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="X8" s="155"/>
-      <c r="Y8" s="162"/>
-      <c r="Z8" s="171"/>
-      <c r="AA8" s="156"/>
-      <c r="AB8" s="172"/>
-      <c r="AC8" s="158"/>
-      <c r="AD8" s="156"/>
-      <c r="AE8" s="172"/>
+      <c r="W8" s="129"/>
+      <c r="X8" s="135"/>
+      <c r="Y8" s="144"/>
+      <c r="Z8" s="129"/>
+      <c r="AA8" s="145"/>
+      <c r="AB8" s="131"/>
+      <c r="AC8" s="129"/>
+      <c r="AD8" s="145"/>
     </row>
-    <row r="9" spans="1:31" ht="30" customHeight="1">
+    <row r="9" spans="1:30" ht="30" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="29"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="63"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="34"/>
       <c r="K9" s="34"/>
       <c r="L9" s="34"/>
       <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="64">
+      <c r="N9" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P9" s="65">
+      <c r="O9" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="62">
+      <c r="P9" s="60">
+        <f>IF(N9=0,0,MAX(0,MIN(N9,$K$1-J9+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R9" s="66">
+      <c r="R9" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S9" s="67">
+      <c r="S9" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T9" s="68">
+      <c r="T9" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U9" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V9" s="177">
+      <c r="U9" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W9" s="182"/>
-      <c r="X9" s="155"/>
-      <c r="Y9" s="162"/>
-      <c r="Z9" s="171"/>
-      <c r="AA9" s="156"/>
-      <c r="AB9" s="172"/>
-      <c r="AC9" s="158"/>
-      <c r="AD9" s="156"/>
-      <c r="AE9" s="172"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="129"/>
+      <c r="X9" s="135"/>
+      <c r="Y9" s="144"/>
+      <c r="Z9" s="129"/>
+      <c r="AA9" s="145"/>
+      <c r="AB9" s="131"/>
+      <c r="AC9" s="129"/>
+      <c r="AD9" s="145"/>
     </row>
-    <row r="10" spans="1:31" ht="30" customHeight="1">
+    <row r="10" spans="1:30" ht="30" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="30"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="64">
+      <c r="C10" s="68"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P10" s="65">
+      <c r="O10" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="62">
+      <c r="P10" s="60">
+        <f>IF(N10=0,0,MAX(0,MIN(N10,$K$1-J10+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R10" s="66">
+      <c r="R10" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S10" s="67">
+      <c r="S10" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T10" s="68">
+      <c r="T10" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U10" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="177">
+      <c r="U10" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="182"/>
-      <c r="X10" s="155"/>
-      <c r="Y10" s="162"/>
-      <c r="Z10" s="171"/>
-      <c r="AA10" s="156"/>
-      <c r="AB10" s="172"/>
-      <c r="AC10" s="158"/>
-      <c r="AD10" s="156"/>
-      <c r="AE10" s="172"/>
+      <c r="V10" s="144"/>
+      <c r="W10" s="129"/>
+      <c r="X10" s="135"/>
+      <c r="Y10" s="144"/>
+      <c r="Z10" s="129"/>
+      <c r="AA10" s="145"/>
+      <c r="AB10" s="131"/>
+      <c r="AC10" s="129"/>
+      <c r="AD10" s="145"/>
     </row>
-    <row r="11" spans="1:31" ht="30" customHeight="1">
+    <row r="11" spans="1:30" ht="30" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="31"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="O11" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="79">
+      <c r="P11" s="77">
+        <f>IF(N11=0,0,MAX(0,MIN(N11,$K$1-J11+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R11" s="80">
+      <c r="R11" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S11" s="67">
+      <c r="S11" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T11" s="68">
+      <c r="T11" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U11" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="177">
+      <c r="U11" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="192"/>
-      <c r="X11" s="193"/>
-      <c r="Y11" s="194"/>
-      <c r="Z11" s="195"/>
-      <c r="AA11" s="196"/>
-      <c r="AB11" s="197"/>
-      <c r="AC11" s="198"/>
-      <c r="AD11" s="196"/>
-      <c r="AE11" s="197"/>
+      <c r="V11" s="164"/>
+      <c r="W11" s="165"/>
+      <c r="X11" s="163"/>
+      <c r="Y11" s="164"/>
+      <c r="Z11" s="165"/>
+      <c r="AA11" s="166"/>
+      <c r="AB11" s="167"/>
+      <c r="AC11" s="165"/>
+      <c r="AD11" s="166"/>
     </row>
-    <row r="12" spans="1:31" ht="30" customHeight="1">
+    <row r="12" spans="1:30" ht="30" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="32">
         <v>2</v>
       </c>
-      <c r="C12" s="81">
+      <c r="C12" s="79">
         <v>0.15</v>
       </c>
-      <c r="D12" s="60" t="s">
+      <c r="D12" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="136" t="s">
+      <c r="E12" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="121"/>
-      <c r="H12" s="61" t="s">
+      <c r="G12" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="82" t="s">
+      <c r="H12" s="60"/>
+      <c r="I12" s="80" t="s">
         <v>42</v>
+      </c>
+      <c r="J12" s="34">
+        <v>46302</v>
       </c>
       <c r="K12" s="34">
         <v>46302</v>
@@ -3612,3076 +3535,3121 @@
       <c r="M12" s="34">
         <v>46302</v>
       </c>
-      <c r="N12" s="34">
-        <v>46302</v>
-      </c>
-      <c r="O12" s="62">
+      <c r="N12" s="60">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="62"/>
-      <c r="R12" s="66">
+      <c r="O12" s="63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="60">
+        <f>IF(N12=0,0,MAX(0,MIN(N12,$K$1-J12+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="64">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="R12" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="67">
+        <v>1</v>
+      </c>
+      <c r="S12" s="66">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="68">
+        <v>1</v>
+      </c>
+      <c r="T12" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="177">
+        <v>1</v>
+      </c>
+      <c r="U12" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="185"/>
-      <c r="X12" s="186" t="s">
+      <c r="V12" s="159"/>
+      <c r="W12" s="157" t="s">
         <v>32</v>
       </c>
-      <c r="Y12" s="187"/>
-      <c r="Z12" s="188"/>
-      <c r="AA12" s="189"/>
-      <c r="AB12" s="190"/>
-      <c r="AC12" s="191"/>
-      <c r="AD12" s="189"/>
-      <c r="AE12" s="190"/>
+      <c r="X12" s="158"/>
+      <c r="Y12" s="159"/>
+      <c r="Z12" s="160"/>
+      <c r="AA12" s="161"/>
+      <c r="AB12" s="162"/>
+      <c r="AC12" s="160"/>
+      <c r="AD12" s="161"/>
     </row>
-    <row r="13" spans="1:31" ht="30" customHeight="1">
+    <row r="13" spans="1:30" ht="30" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="30"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="136" t="s">
+      <c r="C13" s="81"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="124" t="s">
+      <c r="F13" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="125"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="64" t="s">
+      <c r="G13" s="82"/>
+      <c r="H13" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="85" t="s">
+      <c r="I13" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="K13" s="72">
+      <c r="J13" s="70">
         <v>46302</v>
       </c>
-      <c r="L13" s="72">
+      <c r="K13" s="70">
         <v>46302</v>
       </c>
-      <c r="M13" s="72">
+      <c r="L13" s="70">
         <v>46302</v>
       </c>
-      <c r="N13" s="72">
+      <c r="M13" s="70">
         <v>46302</v>
       </c>
-      <c r="O13" s="62">
+      <c r="N13" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="66">
+      <c r="O13" s="63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P13" s="60">
+        <f>IF(N13=0,0,MAX(0,MIN(N13,$K$1-J13+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="64">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="R13" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="67">
+        <v>1</v>
+      </c>
+      <c r="S13" s="66">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="68">
+        <v>1</v>
+      </c>
+      <c r="T13" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="177">
+        <v>1</v>
+      </c>
+      <c r="U13" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="183"/>
-      <c r="X13" s="157" t="s">
+      <c r="V13" s="144"/>
+      <c r="W13" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="Y13" s="162"/>
-      <c r="Z13" s="171"/>
-      <c r="AA13" s="156"/>
-      <c r="AB13" s="172"/>
-      <c r="AC13" s="158"/>
-      <c r="AD13" s="156"/>
-      <c r="AE13" s="172"/>
+      <c r="X13" s="135"/>
+      <c r="Y13" s="144"/>
+      <c r="Z13" s="129"/>
+      <c r="AA13" s="145"/>
+      <c r="AB13" s="131"/>
+      <c r="AC13" s="129"/>
+      <c r="AD13" s="145"/>
     </row>
-    <row r="14" spans="1:31" ht="30" customHeight="1">
+    <row r="14" spans="1:30" ht="30" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="136" t="s">
+      <c r="C14" s="81"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="124" t="s">
+      <c r="F14" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="125"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="64" t="s">
+      <c r="G14" s="82"/>
+      <c r="H14" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J14" s="85" t="s">
+      <c r="I14" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="72">
+      <c r="J14" s="70">
         <v>46302</v>
       </c>
-      <c r="L14" s="72">
+      <c r="K14" s="70">
         <v>46302</v>
       </c>
-      <c r="M14" s="72">
+      <c r="L14" s="70">
         <v>46302</v>
       </c>
-      <c r="N14" s="72">
+      <c r="M14" s="70">
         <v>46302</v>
       </c>
-      <c r="O14" s="62">
+      <c r="N14" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="66">
+      <c r="O14" s="63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P14" s="60">
+        <f>IF(N14=0,0,MAX(0,MIN(N14,$K$1-J14+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="64">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="R14" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="67">
+        <v>1</v>
+      </c>
+      <c r="S14" s="66">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="68">
+        <v>1</v>
+      </c>
+      <c r="T14" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="177">
+        <v>1</v>
+      </c>
+      <c r="U14" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W14" s="183"/>
-      <c r="X14" s="157" t="s">
+      <c r="V14" s="144"/>
+      <c r="W14" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="Y14" s="162"/>
-      <c r="Z14" s="171"/>
-      <c r="AA14" s="156"/>
-      <c r="AB14" s="172"/>
-      <c r="AC14" s="158"/>
-      <c r="AD14" s="156"/>
-      <c r="AE14" s="172"/>
+      <c r="X14" s="135"/>
+      <c r="Y14" s="144"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="145"/>
+      <c r="AB14" s="131"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="145"/>
     </row>
-    <row r="15" spans="1:31" ht="30" customHeight="1">
+    <row r="15" spans="1:30" ht="30" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="30"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="136" t="s">
+      <c r="C15" s="81"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="124" t="s">
+      <c r="F15" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="125"/>
-      <c r="H15" s="84" t="s">
+      <c r="G15" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="85" t="s">
+      <c r="H15" s="62"/>
+      <c r="I15" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="72">
+      <c r="J15" s="70">
         <v>46302</v>
       </c>
-      <c r="L15" s="72">
+      <c r="K15" s="70">
         <v>46302</v>
       </c>
-      <c r="M15" s="72">
+      <c r="L15" s="70">
         <v>46302</v>
       </c>
-      <c r="N15" s="72">
+      <c r="M15" s="70">
         <v>46302</v>
       </c>
-      <c r="O15" s="62">
+      <c r="N15" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="66">
+      <c r="O15" s="63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P15" s="60">
+        <f>IF(N15=0,0,MAX(0,MIN(N15,$K$1-J15+1)))</f>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="64">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="R15" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="67">
+        <v>1</v>
+      </c>
+      <c r="S15" s="66">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="68">
+        <v>1</v>
+      </c>
+      <c r="T15" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="177">
+        <v>1</v>
+      </c>
+      <c r="U15" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" s="183"/>
-      <c r="X15" s="157" t="s">
+      <c r="V15" s="144"/>
+      <c r="W15" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="Y15" s="162"/>
-      <c r="Z15" s="171"/>
-      <c r="AA15" s="156"/>
-      <c r="AB15" s="172"/>
-      <c r="AC15" s="158"/>
-      <c r="AD15" s="156"/>
-      <c r="AE15" s="172"/>
+      <c r="X15" s="135"/>
+      <c r="Y15" s="144"/>
+      <c r="Z15" s="129"/>
+      <c r="AA15" s="145"/>
+      <c r="AB15" s="131"/>
+      <c r="AC15" s="129"/>
+      <c r="AD15" s="145"/>
     </row>
-    <row r="16" spans="1:31" ht="30" customHeight="1">
+    <row r="16" spans="1:30" ht="30" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="30"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="85"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="62">
+      <c r="C16" s="81"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P16" s="65">
+      <c r="O16" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="60">
+        <f>IF(N16=0,0,MAX(0,MIN(N16,$K$1-J16+1)))</f>
         <v>0</v>
       </c>
       <c r="Q16" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R16" s="66">
+      <c r="R16" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S16" s="67">
+      <c r="S16" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T16" s="68">
+      <c r="T16" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U16" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="177">
+      <c r="U16" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="183"/>
-      <c r="X16" s="157"/>
-      <c r="Y16" s="162"/>
-      <c r="Z16" s="171"/>
-      <c r="AA16" s="156"/>
-      <c r="AB16" s="172"/>
-      <c r="AC16" s="158"/>
-      <c r="AD16" s="156"/>
-      <c r="AE16" s="172"/>
+      <c r="V16" s="144"/>
+      <c r="W16" s="133"/>
+      <c r="X16" s="135"/>
+      <c r="Y16" s="144"/>
+      <c r="Z16" s="129"/>
+      <c r="AA16" s="145"/>
+      <c r="AB16" s="131"/>
+      <c r="AC16" s="129"/>
+      <c r="AD16" s="145"/>
     </row>
-    <row r="17" spans="1:31" ht="30" customHeight="1">
+    <row r="17" spans="1:30" ht="30" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="79">
+      <c r="C17" s="84"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P17" s="78">
+      <c r="O17" s="76">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="76">
+      <c r="P17" s="74">
+        <f>IF(N17=0,0,MAX(0,MIN(N17,$K$1-J17+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R17" s="80">
+      <c r="R17" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S17" s="67">
+      <c r="S17" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T17" s="68">
+      <c r="T17" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U17" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="177">
+      <c r="U17" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="200"/>
-      <c r="X17" s="201"/>
-      <c r="Y17" s="194"/>
-      <c r="Z17" s="195"/>
-      <c r="AA17" s="196"/>
-      <c r="AB17" s="197"/>
-      <c r="AC17" s="198"/>
-      <c r="AD17" s="196"/>
-      <c r="AE17" s="197"/>
+      <c r="V17" s="164"/>
+      <c r="W17" s="165"/>
+      <c r="X17" s="163"/>
+      <c r="Y17" s="164"/>
+      <c r="Z17" s="165"/>
+      <c r="AA17" s="166"/>
+      <c r="AB17" s="167"/>
+      <c r="AC17" s="165"/>
+      <c r="AD17" s="166"/>
     </row>
-    <row r="18" spans="1:31" ht="30" customHeight="1">
+    <row r="18" spans="1:30" ht="30" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="30">
         <v>3</v>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="79">
         <v>0.4</v>
       </c>
-      <c r="D18" s="134" t="s">
+      <c r="D18" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="136" t="s">
+      <c r="E18" s="112" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="120" t="s">
+      <c r="F18" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="121"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62" t="s">
+      <c r="G18" s="59"/>
+      <c r="H18" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J18" s="82" t="s">
+      <c r="I18" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="K18" s="34">
+      <c r="J18" s="34">
         <v>46303</v>
       </c>
-      <c r="L18" s="35">
+      <c r="K18" s="35">
         <v>46303</v>
       </c>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="62">
+      <c r="L18" s="34"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="60">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P18" s="65">
+      <c r="O18" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="62">
+      <c r="P18" s="60">
+        <f>IF(N18=0,0,MAX(0,MIN(N18,$K$1-J18+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R18" s="66">
+      <c r="R18" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S18" s="67">
+      <c r="S18" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T18" s="68">
+      <c r="T18" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U18" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="177">
+      <c r="U18" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W18" s="188"/>
-      <c r="X18" s="189"/>
-      <c r="Y18" s="199" t="s">
+      <c r="V18" s="159"/>
+      <c r="W18" s="160"/>
+      <c r="X18" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="Z18" s="188"/>
-      <c r="AA18" s="189"/>
-      <c r="AB18" s="190"/>
-      <c r="AC18" s="191"/>
-      <c r="AD18" s="189"/>
-      <c r="AE18" s="190"/>
+      <c r="Y18" s="159"/>
+      <c r="Z18" s="160"/>
+      <c r="AA18" s="161"/>
+      <c r="AB18" s="162"/>
+      <c r="AC18" s="160"/>
+      <c r="AD18" s="161"/>
     </row>
-    <row r="19" spans="1:31" ht="30" customHeight="1">
+    <row r="19" spans="1:30" ht="30" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="30"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="134"/>
-      <c r="E19" s="136" t="s">
+      <c r="C19" s="81"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="135" t="s">
+      <c r="F19" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="124"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="95" t="s">
+      <c r="G19" s="92"/>
+      <c r="H19" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="96" t="s">
+      <c r="I19" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="34">
+      <c r="J19" s="34">
         <v>46303</v>
       </c>
-      <c r="L19" s="35">
+      <c r="K19" s="35">
         <v>46303</v>
       </c>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="67">
-        <f t="shared" ref="S19" si="9">IFERROR(Q19/O19,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T19" s="68">
-        <f t="shared" ref="T19" si="10">IFERROR(R19/O19,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="69">
-        <f t="shared" ref="U19" si="11">IF(OR(O19=0,R19=0),0,MIN(1,R19/O19))</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="177">
-        <f t="shared" ref="V19" si="12">U19-S19</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="171"/>
-      <c r="X19" s="156"/>
-      <c r="Y19" s="163" t="s">
+      <c r="L19" s="34"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O19" s="63"/>
+      <c r="P19" s="60">
+        <f>IF(N19=0,0,MAX(0,MIN(N19,$K$1-J19+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="65">
+        <f t="shared" ref="R19" si="8">IFERROR(P19/N19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="66">
+        <f t="shared" ref="S19" si="9">IFERROR(Q19/N19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="67">
+        <f t="shared" ref="T19" si="10">IF(OR(N19=0,Q19=0),0,MIN(1,Q19/N19))</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="150">
+        <f t="shared" ref="U19" si="11">T19-R19</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="144"/>
+      <c r="W19" s="129"/>
+      <c r="X19" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="Z19" s="171"/>
-      <c r="AA19" s="156"/>
-      <c r="AB19" s="172"/>
-      <c r="AC19" s="158"/>
-      <c r="AD19" s="156"/>
-      <c r="AE19" s="172"/>
+      <c r="Y19" s="144"/>
+      <c r="Z19" s="129"/>
+      <c r="AA19" s="145"/>
+      <c r="AB19" s="131"/>
+      <c r="AC19" s="129"/>
+      <c r="AD19" s="145"/>
     </row>
-    <row r="20" spans="1:31" ht="30" customHeight="1">
+    <row r="20" spans="1:30" ht="30" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="30"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="136" t="s">
+      <c r="C20" s="81"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="128" t="s">
+      <c r="F20" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="129"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91" t="s">
+      <c r="G20" s="88"/>
+      <c r="H20" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="92" t="s">
+      <c r="I20" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="K20" s="34">
+      <c r="J20" s="34">
         <v>46303</v>
       </c>
-      <c r="L20" s="35">
+      <c r="K20" s="35">
         <v>46303</v>
       </c>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="64">
+      <c r="L20" s="34"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P20" s="65">
+      <c r="O20" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="60">
+        <f>IF(N20=0,0,MAX(0,MIN(N20,$K$1-J20+1)))</f>
         <v>0</v>
       </c>
       <c r="Q20" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R20" s="66">
+      <c r="R20" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S20" s="93">
+      <c r="S20" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T20" s="68">
+      <c r="T20" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U20" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="177">
+      <c r="U20" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W20" s="171"/>
-      <c r="X20" s="160"/>
-      <c r="Y20" s="164" t="s">
+      <c r="V20" s="144"/>
+      <c r="W20" s="133"/>
+      <c r="X20" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="160"/>
-      <c r="AB20" s="174"/>
-      <c r="AC20" s="167"/>
-      <c r="AD20" s="160"/>
-      <c r="AE20" s="174"/>
+      <c r="Y20" s="146"/>
+      <c r="Z20" s="133"/>
+      <c r="AA20" s="147"/>
+      <c r="AB20" s="140"/>
+      <c r="AC20" s="133"/>
+      <c r="AD20" s="147"/>
     </row>
-    <row r="21" spans="1:31" ht="30" customHeight="1">
+    <row r="21" spans="1:30" ht="30" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="30"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="136" t="s">
+      <c r="C21" s="81"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="112" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="126" t="s">
+      <c r="F21" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="127"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="76" t="s">
+      <c r="G21" s="85"/>
+      <c r="H21" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="J21" s="88" t="s">
+      <c r="I21" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="K21" s="36">
+      <c r="J21" s="36">
         <v>46303</v>
       </c>
-      <c r="L21" s="37">
+      <c r="K21" s="37">
         <v>46303</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="37"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="74">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="O21" s="76">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="P21" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="76">
+      <c r="P21" s="74">
+        <f>IF(N21=0,0,MAX(0,MIN(N21,$K$1-J21+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R21" s="80">
+      <c r="R21" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S21" s="67">
+      <c r="S21" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T21" s="68">
+      <c r="T21" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U21" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="177">
+      <c r="U21" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W21" s="195"/>
-      <c r="X21" s="196"/>
-      <c r="Y21" s="202" t="s">
+      <c r="V21" s="164"/>
+      <c r="W21" s="165"/>
+      <c r="X21" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="Z21" s="195"/>
-      <c r="AA21" s="196"/>
-      <c r="AB21" s="197"/>
-      <c r="AC21" s="198"/>
-      <c r="AD21" s="196"/>
-      <c r="AE21" s="197"/>
+      <c r="Y21" s="164"/>
+      <c r="Z21" s="165"/>
+      <c r="AA21" s="166"/>
+      <c r="AB21" s="167"/>
+      <c r="AC21" s="165"/>
+      <c r="AD21" s="166"/>
     </row>
-    <row r="22" spans="1:31" ht="30" customHeight="1">
+    <row r="22" spans="1:30" ht="30" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="30"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="136" t="s">
+      <c r="C22" s="81"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="120" t="s">
+      <c r="F22" s="105" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="121"/>
-      <c r="H22" s="61" t="s">
+      <c r="G22" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="82" t="s">
+      <c r="H22" s="60"/>
+      <c r="I22" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="K22" s="34">
+      <c r="J22" s="34">
         <v>46303</v>
       </c>
-      <c r="L22" s="35">
+      <c r="K22" s="35">
         <v>46303</v>
       </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="62">
+      <c r="L22" s="34"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="60">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P22" s="65">
+      <c r="O22" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="62">
+      <c r="P22" s="60">
+        <f>IF(N22=0,0,MAX(0,MIN(N22,$K$1-J22+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R22" s="66">
+      <c r="R22" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S22" s="67">
+      <c r="S22" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T22" s="68">
+      <c r="T22" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U22" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="177">
+      <c r="U22" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W22" s="188"/>
-      <c r="X22" s="189"/>
-      <c r="Y22" s="199" t="s">
+      <c r="V22" s="159"/>
+      <c r="W22" s="160"/>
+      <c r="X22" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="Z22" s="188"/>
-      <c r="AA22" s="189"/>
-      <c r="AB22" s="190"/>
-      <c r="AC22" s="191"/>
-      <c r="AD22" s="189"/>
-      <c r="AE22" s="190"/>
+      <c r="Y22" s="159"/>
+      <c r="Z22" s="160"/>
+      <c r="AA22" s="161"/>
+      <c r="AB22" s="162"/>
+      <c r="AC22" s="160"/>
+      <c r="AD22" s="161"/>
     </row>
-    <row r="23" spans="1:31" ht="30" customHeight="1">
+    <row r="23" spans="1:30" ht="30" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="30"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="136" t="s">
+      <c r="C23" s="81"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="112" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="139" t="s">
+      <c r="F23" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="128"/>
-      <c r="H23" s="61" t="s">
+      <c r="G23" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I23" s="62"/>
-      <c r="J23" s="140" t="s">
+      <c r="H23" s="60"/>
+      <c r="I23" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="K23" s="34">
+      <c r="J23" s="34">
         <v>46303</v>
       </c>
-      <c r="L23" s="35">
+      <c r="K23" s="35">
         <v>46303</v>
       </c>
-      <c r="M23" s="38"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="69"/>
-      <c r="V23" s="177"/>
-      <c r="W23" s="171"/>
-      <c r="X23" s="156"/>
-      <c r="Y23" s="163"/>
-      <c r="Z23" s="171"/>
-      <c r="AA23" s="156"/>
-      <c r="AB23" s="172"/>
-      <c r="AC23" s="158"/>
-      <c r="AD23" s="156"/>
-      <c r="AE23" s="172"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O23" s="63"/>
+      <c r="P23" s="60">
+        <f>IF(N23=0,0,MAX(0,MIN(N23,$K$1-J23+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="65">
+        <f t="shared" ref="R23:R26" si="12">IFERROR(P23/N23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="66">
+        <f t="shared" ref="S23:S26" si="13">IFERROR(Q23/N23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T23" s="67">
+        <f t="shared" ref="T23:T26" si="14">IF(OR(N23=0,Q23=0),0,MIN(1,Q23/N23))</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="150">
+        <f t="shared" ref="U23:U26" si="15">T23-R23</f>
+        <v>0</v>
+      </c>
+      <c r="V23" s="144"/>
+      <c r="W23" s="129"/>
+      <c r="X23" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y23" s="144"/>
+      <c r="Z23" s="129"/>
+      <c r="AA23" s="145"/>
+      <c r="AB23" s="131"/>
+      <c r="AC23" s="129"/>
+      <c r="AD23" s="145"/>
     </row>
-    <row r="24" spans="1:31" ht="30" customHeight="1">
+    <row r="24" spans="1:30" ht="30" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="30"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="136" t="s">
+      <c r="C24" s="81"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="112" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="139" t="s">
+      <c r="F24" s="115" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="128"/>
-      <c r="H24" s="61" t="s">
+      <c r="G24" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="141" t="s">
+      <c r="H24" s="60"/>
+      <c r="I24" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="K24" s="34">
+      <c r="J24" s="34">
         <v>46303</v>
       </c>
-      <c r="L24" s="35">
+      <c r="K24" s="35">
         <v>46303</v>
       </c>
-      <c r="M24" s="38"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="65"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="67"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="177"/>
-      <c r="W24" s="171"/>
-      <c r="X24" s="156"/>
-      <c r="Y24" s="163"/>
-      <c r="Z24" s="171"/>
-      <c r="AA24" s="156"/>
-      <c r="AB24" s="172"/>
-      <c r="AC24" s="158"/>
-      <c r="AD24" s="156"/>
-      <c r="AE24" s="172"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O24" s="63"/>
+      <c r="P24" s="60">
+        <f>IF(N24=0,0,MAX(0,MIN(N24,$K$1-J24+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="65">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="66">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="67">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="150">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="144"/>
+      <c r="W24" s="129"/>
+      <c r="X24" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y24" s="144"/>
+      <c r="Z24" s="129"/>
+      <c r="AA24" s="145"/>
+      <c r="AB24" s="131"/>
+      <c r="AC24" s="129"/>
+      <c r="AD24" s="145"/>
     </row>
-    <row r="25" spans="1:31" ht="30" customHeight="1">
+    <row r="25" spans="1:30" ht="30" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="30"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="134"/>
-      <c r="E25" s="136" t="s">
+      <c r="C25" s="81"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="112" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="139" t="s">
+      <c r="F25" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="128"/>
-      <c r="H25" s="61" t="s">
+      <c r="G25" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="141" t="s">
+      <c r="H25" s="60"/>
+      <c r="I25" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="34">
+      <c r="J25" s="34">
         <v>46303</v>
       </c>
-      <c r="L25" s="35">
+      <c r="K25" s="35">
         <v>46303</v>
       </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="62">
+      <c r="L25" s="34"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P25" s="65">
+      <c r="O25" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="62">
+      <c r="P25" s="60">
+        <f>IF(N25=0,0,MAX(0,MIN(N25,$K$1-J25+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R25" s="66">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="67">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="68">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="177">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="171"/>
-      <c r="X25" s="156"/>
-      <c r="Y25" s="163" t="s">
+      <c r="R25" s="65">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="66">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="67">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="150">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="144"/>
+      <c r="W25" s="129"/>
+      <c r="X25" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="Z25" s="171"/>
-      <c r="AA25" s="156"/>
-      <c r="AB25" s="172"/>
-      <c r="AC25" s="158"/>
-      <c r="AD25" s="156"/>
-      <c r="AE25" s="172"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="129"/>
+      <c r="AA25" s="145"/>
+      <c r="AB25" s="131"/>
+      <c r="AC25" s="129"/>
+      <c r="AD25" s="145"/>
     </row>
-    <row r="26" spans="1:31" ht="30" customHeight="1">
+    <row r="26" spans="1:30" ht="30" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="30"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="136" t="s">
+      <c r="C26" s="81"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="139" t="s">
+      <c r="F26" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="128"/>
-      <c r="H26" s="61" t="s">
+      <c r="G26" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="142" t="s">
+      <c r="H26" s="60"/>
+      <c r="I26" s="118" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="34">
+      <c r="J26" s="34">
         <v>46303</v>
       </c>
-      <c r="L26" s="35">
+      <c r="K26" s="35">
         <v>46303</v>
       </c>
-      <c r="M26" s="38"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="95"/>
-      <c r="P26" s="137"/>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="138"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="68"/>
-      <c r="U26" s="69"/>
-      <c r="V26" s="177"/>
-      <c r="W26" s="171"/>
-      <c r="X26" s="156"/>
-      <c r="Y26" s="163"/>
-      <c r="Z26" s="171"/>
-      <c r="AA26" s="156"/>
-      <c r="AB26" s="172"/>
-      <c r="AC26" s="158"/>
-      <c r="AD26" s="156"/>
-      <c r="AE26" s="172"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O26" s="113"/>
+      <c r="P26" s="60">
+        <f>IF(N26=0,0,MAX(0,MIN(N26,$K$1-J26+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="65">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="66">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="67">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="150">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="144"/>
+      <c r="W26" s="129"/>
+      <c r="X26" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y26" s="144"/>
+      <c r="Z26" s="129"/>
+      <c r="AA26" s="145"/>
+      <c r="AB26" s="131"/>
+      <c r="AC26" s="129"/>
+      <c r="AD26" s="145"/>
     </row>
-    <row r="27" spans="1:31" ht="30" customHeight="1">
+    <row r="27" spans="1:30" ht="30" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="30"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="136" t="s">
+      <c r="C27" s="81"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="127"/>
-      <c r="H27" s="87" t="s">
+      <c r="G27" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="76"/>
-      <c r="J27" s="88" t="s">
+      <c r="H27" s="74"/>
+      <c r="I27" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="K27" s="40">
+      <c r="J27" s="38">
         <v>46303</v>
       </c>
-      <c r="L27" s="41">
+      <c r="K27" s="39">
         <v>46303</v>
       </c>
-      <c r="M27" s="40"/>
-      <c r="N27" s="41"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="74">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="O27" s="76">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="P27" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="76">
+      <c r="P27" s="74">
+        <f>IF(N27=0,0,MAX(0,MIN(N27,$K$1-J27+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R27" s="80">
+      <c r="R27" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S27" s="67">
+      <c r="S27" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T27" s="68">
+      <c r="T27" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U27" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="177">
+      <c r="U27" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W27" s="195"/>
-      <c r="X27" s="196"/>
-      <c r="Y27" s="202" t="s">
+      <c r="V27" s="164"/>
+      <c r="W27" s="165"/>
+      <c r="X27" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="Z27" s="195"/>
-      <c r="AA27" s="196"/>
-      <c r="AB27" s="197"/>
-      <c r="AC27" s="198"/>
-      <c r="AD27" s="196"/>
-      <c r="AE27" s="197"/>
+      <c r="Y27" s="164"/>
+      <c r="Z27" s="165"/>
+      <c r="AA27" s="166"/>
+      <c r="AB27" s="167"/>
+      <c r="AC27" s="165"/>
+      <c r="AD27" s="166"/>
     </row>
-    <row r="28" spans="1:31" ht="30" customHeight="1">
+    <row r="28" spans="1:30" ht="30" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="30"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="136" t="s">
+      <c r="C28" s="81"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="120" t="s">
+      <c r="F28" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="121"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="62" t="s">
+      <c r="G28" s="59"/>
+      <c r="H28" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="82" t="s">
+      <c r="I28" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="K28" s="34">
+      <c r="J28" s="34">
         <v>46303</v>
       </c>
-      <c r="L28" s="35">
+      <c r="K28" s="35">
         <v>46303</v>
       </c>
-      <c r="M28" s="34"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="62">
+      <c r="L28" s="34"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="60">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P28" s="65">
+      <c r="O28" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="62">
+      <c r="P28" s="60">
+        <f>IF(N28=0,0,MAX(0,MIN(N28,$K$1-J28+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R28" s="66">
+      <c r="R28" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S28" s="67">
+      <c r="S28" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T28" s="68">
+      <c r="T28" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U28" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="177">
+      <c r="U28" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="188"/>
-      <c r="X28" s="189"/>
-      <c r="Y28" s="199" t="s">
+      <c r="V28" s="159"/>
+      <c r="W28" s="160"/>
+      <c r="X28" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="Z28" s="188"/>
-      <c r="AA28" s="189"/>
-      <c r="AB28" s="190"/>
-      <c r="AC28" s="191"/>
-      <c r="AD28" s="189"/>
-      <c r="AE28" s="190"/>
+      <c r="Y28" s="159"/>
+      <c r="Z28" s="160"/>
+      <c r="AA28" s="161"/>
+      <c r="AB28" s="162"/>
+      <c r="AC28" s="160"/>
+      <c r="AD28" s="161"/>
     </row>
-    <row r="29" spans="1:31" ht="30" customHeight="1">
+    <row r="29" spans="1:30" ht="30" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="30"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="136" t="s">
+      <c r="C29" s="81"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="144" t="s">
+      <c r="F29" s="120" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="124"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="64" t="s">
+      <c r="G29" s="82"/>
+      <c r="H29" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J29" s="85" t="s">
+      <c r="I29" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="K29" s="34">
+      <c r="J29" s="34">
         <v>46307</v>
       </c>
-      <c r="L29" s="35">
+      <c r="K29" s="35">
         <v>46307</v>
       </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="64">
+      <c r="L29" s="34"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P29" s="65">
+      <c r="O29" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="60">
+        <f>IF(N29=0,0,MAX(0,MIN(N29,$K$1-J29+1)))</f>
         <v>0</v>
       </c>
       <c r="Q29" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R29" s="66">
+      <c r="R29" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S29" s="67">
+      <c r="S29" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T29" s="68">
+      <c r="T29" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U29" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V29" s="177">
+      <c r="U29" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W29" s="171"/>
-      <c r="X29" s="156"/>
-      <c r="Y29" s="163"/>
-      <c r="Z29" s="175"/>
-      <c r="AA29" s="156"/>
-      <c r="AB29" s="176"/>
-      <c r="AC29" s="168" t="s">
+      <c r="V29" s="144"/>
+      <c r="W29" s="129"/>
+      <c r="X29" s="136"/>
+      <c r="Y29" s="148"/>
+      <c r="Z29" s="129"/>
+      <c r="AA29" s="149"/>
+      <c r="AB29" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD29" s="156"/>
-      <c r="AE29" s="172"/>
+      <c r="AC29" s="129"/>
+      <c r="AD29" s="145"/>
     </row>
-    <row r="30" spans="1:31" ht="30" customHeight="1">
+    <row r="30" spans="1:30" ht="30" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="30"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="136" t="s">
+      <c r="C30" s="81"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="144" t="s">
+      <c r="F30" s="120" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="124"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="64" t="s">
+      <c r="G30" s="82"/>
+      <c r="H30" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J30" s="85" t="s">
+      <c r="I30" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="K30" s="34">
+      <c r="J30" s="34">
         <v>46307</v>
       </c>
-      <c r="L30" s="35">
+      <c r="K30" s="35">
         <v>46307</v>
       </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="64">
+      <c r="L30" s="34"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P30" s="65">
+      <c r="O30" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="60">
+        <f>IF(N30=0,0,MAX(0,MIN(N30,$K$1-J30+1)))</f>
         <v>0</v>
       </c>
       <c r="Q30" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R30" s="66">
+      <c r="R30" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S30" s="67">
+      <c r="S30" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T30" s="68">
+      <c r="T30" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U30" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="177">
+      <c r="U30" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W30" s="171"/>
-      <c r="X30" s="156"/>
-      <c r="Y30" s="163"/>
-      <c r="Z30" s="175"/>
-      <c r="AA30" s="159"/>
-      <c r="AB30" s="176"/>
-      <c r="AC30" s="168" t="s">
+      <c r="V30" s="144"/>
+      <c r="W30" s="129"/>
+      <c r="X30" s="136"/>
+      <c r="Y30" s="148"/>
+      <c r="Z30" s="132"/>
+      <c r="AA30" s="149"/>
+      <c r="AB30" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD30" s="159"/>
-      <c r="AE30" s="172"/>
+      <c r="AC30" s="132"/>
+      <c r="AD30" s="145"/>
     </row>
-    <row r="31" spans="1:31" ht="30" customHeight="1">
+    <row r="31" spans="1:30" ht="30" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="30"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="136" t="s">
+      <c r="C31" s="81"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="112" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="144" t="s">
+      <c r="F31" s="120" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="124"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="64" t="s">
+      <c r="G31" s="82"/>
+      <c r="H31" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J31" s="85" t="s">
+      <c r="I31" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="K31" s="34">
+      <c r="J31" s="34">
         <v>46307</v>
       </c>
-      <c r="L31" s="35">
+      <c r="K31" s="35">
         <v>46307</v>
       </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="64">
+      <c r="L31" s="34"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P31" s="65">
+      <c r="O31" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="60">
+        <f>IF(N31=0,0,MAX(0,MIN(N31,$K$1-J31+1)))</f>
         <v>0</v>
       </c>
       <c r="Q31" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R31" s="66">
+      <c r="R31" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S31" s="67">
+      <c r="S31" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T31" s="68">
+      <c r="T31" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U31" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V31" s="177">
+      <c r="U31" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W31" s="171"/>
-      <c r="X31" s="156"/>
-      <c r="Y31" s="162"/>
-      <c r="Z31" s="175"/>
-      <c r="AA31" s="156"/>
-      <c r="AB31" s="176"/>
-      <c r="AC31" s="168" t="s">
+      <c r="V31" s="144"/>
+      <c r="W31" s="129"/>
+      <c r="X31" s="135"/>
+      <c r="Y31" s="148"/>
+      <c r="Z31" s="129"/>
+      <c r="AA31" s="149"/>
+      <c r="AB31" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD31" s="156"/>
-      <c r="AE31" s="176"/>
+      <c r="AC31" s="129"/>
+      <c r="AD31" s="149"/>
     </row>
-    <row r="32" spans="1:31" ht="30" customHeight="1">
+    <row r="32" spans="1:30" ht="30" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="30"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="136" t="s">
+      <c r="C32" s="81"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="112" t="s">
         <v>100</v>
       </c>
-      <c r="F32" s="144" t="s">
+      <c r="F32" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="124"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="64" t="s">
+      <c r="G32" s="88"/>
+      <c r="H32" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J32" s="92" t="s">
+      <c r="I32" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="K32" s="34">
+      <c r="J32" s="34">
         <v>46307</v>
       </c>
-      <c r="L32" s="35">
+      <c r="K32" s="35">
         <v>46307</v>
       </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="64">
-        <f t="shared" ref="O32:O45" si="13">IF(OR(K32="",L32=""),0,L32-K32+1)</f>
-        <v>1</v>
-      </c>
-      <c r="P32" s="65">
-        <f t="shared" ref="P32:P45" si="14">IF(OR(M32="",N32=""),0,N32-M32+1)</f>
+      <c r="L32" s="34"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O32" s="63">
+        <f t="shared" ref="O32:O45" si="16">IF(OR(L32="",M32=""),0,M32-L32+1)</f>
+        <v>0</v>
+      </c>
+      <c r="P32" s="60">
+        <f>IF(N32=0,0,MAX(0,MIN(N32,$K$1-J32+1)))</f>
         <v>0</v>
       </c>
       <c r="Q32" s="64">
-        <f t="shared" ref="Q32:Q45" si="15">IF(O32=0,0,MAX(0,MIN(O32,$L$1-K32+1)))</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="66">
-        <f t="shared" ref="R32:R45" si="16">IF(P32=0,0,MIN(P32,O32))</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="67">
-        <f t="shared" ref="S32:S45" si="17">IFERROR(Q32/O32,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="68">
-        <f t="shared" ref="T32:T45" si="18">IFERROR(R32/O32,0)</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="69">
-        <f t="shared" ref="U32:U45" si="19">IF(OR(O32=0,R32=0),0,MIN(1,R32/O32))</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="177">
-        <f t="shared" ref="V32:V45" si="20">U32-S32</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="171"/>
-      <c r="X32" s="156"/>
-      <c r="Y32" s="162"/>
-      <c r="Z32" s="175"/>
-      <c r="AA32" s="156"/>
-      <c r="AB32" s="176"/>
-      <c r="AC32" s="168" t="s">
+        <f t="shared" ref="Q32:Q45" si="17">IF(O32=0,0,MIN(O32,N32))</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="65">
+        <f t="shared" ref="R32:R45" si="18">IFERROR(P32/N32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="66">
+        <f t="shared" ref="S32:S45" si="19">IFERROR(Q32/N32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T32" s="67">
+        <f t="shared" ref="T32:T45" si="20">IF(OR(N32=0,Q32=0),0,MIN(1,Q32/N32))</f>
+        <v>0</v>
+      </c>
+      <c r="U32" s="150">
+        <f t="shared" ref="U32:U45" si="21">T32-R32</f>
+        <v>0</v>
+      </c>
+      <c r="V32" s="144"/>
+      <c r="W32" s="129"/>
+      <c r="X32" s="135"/>
+      <c r="Y32" s="148"/>
+      <c r="Z32" s="129"/>
+      <c r="AA32" s="149"/>
+      <c r="AB32" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD32" s="156"/>
-      <c r="AE32" s="176"/>
+      <c r="AC32" s="129"/>
+      <c r="AD32" s="149"/>
     </row>
-    <row r="33" spans="1:31" ht="30" customHeight="1">
+    <row r="33" spans="1:30" ht="30" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="30"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="136" t="s">
+      <c r="C33" s="81"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="F33" s="144" t="s">
+      <c r="F33" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="124"/>
-      <c r="H33" s="90"/>
-      <c r="I33" s="64" t="s">
+      <c r="G33" s="88"/>
+      <c r="H33" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J33" s="92" t="s">
+      <c r="I33" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="K33" s="34">
+      <c r="J33" s="34">
         <v>46307</v>
       </c>
-      <c r="L33" s="35">
+      <c r="K33" s="35">
         <v>46307</v>
       </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P33" s="65">
-        <f t="shared" si="14"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O33" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="60">
+        <f>IF(N33=0,0,MAX(0,MIN(N33,$K$1-J33+1)))</f>
         <v>0</v>
       </c>
       <c r="Q33" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R33" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S33" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T33" s="68">
+      <c r="R33" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U33" s="69">
+      <c r="S33" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V33" s="177">
+      <c r="T33" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W33" s="171"/>
-      <c r="X33" s="156"/>
-      <c r="Y33" s="162"/>
-      <c r="Z33" s="175"/>
-      <c r="AA33" s="156"/>
-      <c r="AB33" s="176"/>
-      <c r="AC33" s="168" t="s">
+      <c r="U33" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="144"/>
+      <c r="W33" s="129"/>
+      <c r="X33" s="135"/>
+      <c r="Y33" s="148"/>
+      <c r="Z33" s="129"/>
+      <c r="AA33" s="149"/>
+      <c r="AB33" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD33" s="156"/>
-      <c r="AE33" s="176"/>
+      <c r="AC33" s="129"/>
+      <c r="AD33" s="149"/>
     </row>
-    <row r="34" spans="1:31" ht="30" customHeight="1">
+    <row r="34" spans="1:30" ht="30" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="30"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="136" t="s">
+      <c r="C34" s="81"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="144" t="s">
+      <c r="F34" s="120" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="124"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="64" t="s">
+      <c r="G34" s="88"/>
+      <c r="H34" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J34" s="92" t="s">
+      <c r="I34" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="K34" s="34">
+      <c r="J34" s="34">
         <v>46307</v>
       </c>
-      <c r="L34" s="35">
+      <c r="K34" s="35">
         <v>46307</v>
       </c>
-      <c r="M34" s="34"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P34" s="65">
-        <f t="shared" si="14"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O34" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="60">
+        <f>IF(N34=0,0,MAX(0,MIN(N34,$K$1-J34+1)))</f>
         <v>0</v>
       </c>
       <c r="Q34" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T34" s="68">
+      <c r="R34" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U34" s="69">
+      <c r="S34" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V34" s="177">
+      <c r="T34" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W34" s="171"/>
-      <c r="X34" s="156"/>
-      <c r="Y34" s="162"/>
-      <c r="Z34" s="175"/>
-      <c r="AA34" s="156"/>
-      <c r="AB34" s="176"/>
-      <c r="AC34" s="168" t="s">
+      <c r="U34" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="144"/>
+      <c r="W34" s="129"/>
+      <c r="X34" s="135"/>
+      <c r="Y34" s="148"/>
+      <c r="Z34" s="129"/>
+      <c r="AA34" s="149"/>
+      <c r="AB34" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD34" s="156"/>
-      <c r="AE34" s="176"/>
+      <c r="AC34" s="129"/>
+      <c r="AD34" s="149"/>
     </row>
-    <row r="35" spans="1:31" ht="30" customHeight="1">
+    <row r="35" spans="1:30" ht="30" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="30"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="136" t="s">
+      <c r="C35" s="81"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="144" t="s">
+      <c r="F35" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="124"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="64" t="s">
+      <c r="G35" s="88"/>
+      <c r="H35" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J35" s="92" t="s">
+      <c r="I35" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="K35" s="34">
+      <c r="J35" s="34">
         <v>46307</v>
       </c>
-      <c r="L35" s="35">
+      <c r="K35" s="35">
         <v>46307</v>
       </c>
-      <c r="M35" s="34"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P35" s="65">
-        <f t="shared" si="14"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O35" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="60">
+        <f>IF(N35=0,0,MAX(0,MIN(N35,$K$1-J35+1)))</f>
         <v>0</v>
       </c>
       <c r="Q35" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R35" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T35" s="68">
+      <c r="R35" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U35" s="69">
+      <c r="S35" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V35" s="177">
+      <c r="T35" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W35" s="171"/>
-      <c r="X35" s="156"/>
-      <c r="Y35" s="162"/>
-      <c r="Z35" s="175"/>
-      <c r="AA35" s="156"/>
-      <c r="AB35" s="176"/>
-      <c r="AC35" s="168" t="s">
+      <c r="U35" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="144"/>
+      <c r="W35" s="129"/>
+      <c r="X35" s="135"/>
+      <c r="Y35" s="148"/>
+      <c r="Z35" s="129"/>
+      <c r="AA35" s="149"/>
+      <c r="AB35" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD35" s="156"/>
-      <c r="AE35" s="176"/>
+      <c r="AC35" s="129"/>
+      <c r="AD35" s="149"/>
     </row>
-    <row r="36" spans="1:31" ht="30" customHeight="1">
+    <row r="36" spans="1:30" ht="30" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="30"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="134"/>
-      <c r="E36" s="136" t="s">
+      <c r="C36" s="81"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="144" t="s">
+      <c r="F36" s="120" t="s">
         <v>142</v>
       </c>
-      <c r="G36" s="124"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="64" t="s">
+      <c r="G36" s="88"/>
+      <c r="H36" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J36" s="92" t="s">
+      <c r="I36" s="90" t="s">
         <v>132</v>
       </c>
-      <c r="K36" s="34">
+      <c r="J36" s="34">
         <v>46307</v>
       </c>
-      <c r="L36" s="35">
+      <c r="K36" s="35">
         <v>46307</v>
       </c>
-      <c r="M36" s="34"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P36" s="65">
-        <f t="shared" si="14"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O36" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="60">
+        <f>IF(N36=0,0,MAX(0,MIN(N36,$K$1-J36+1)))</f>
         <v>0</v>
       </c>
       <c r="Q36" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T36" s="68">
+      <c r="R36" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U36" s="69">
+      <c r="S36" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V36" s="177">
+      <c r="T36" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W36" s="171"/>
-      <c r="X36" s="156"/>
-      <c r="Y36" s="162"/>
-      <c r="Z36" s="175"/>
-      <c r="AA36" s="156"/>
-      <c r="AB36" s="176"/>
-      <c r="AC36" s="168" t="s">
+      <c r="U36" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="144"/>
+      <c r="W36" s="129"/>
+      <c r="X36" s="135"/>
+      <c r="Y36" s="148"/>
+      <c r="Z36" s="129"/>
+      <c r="AA36" s="149"/>
+      <c r="AB36" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD36" s="156"/>
-      <c r="AE36" s="176"/>
+      <c r="AC36" s="129"/>
+      <c r="AD36" s="149"/>
     </row>
-    <row r="37" spans="1:31" ht="30" customHeight="1">
+    <row r="37" spans="1:30" ht="30" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="30"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="134"/>
-      <c r="E37" s="136" t="s">
+      <c r="C37" s="81"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="112" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="144" t="s">
+      <c r="F37" s="120" t="s">
         <v>143</v>
       </c>
-      <c r="G37" s="124"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="64" t="s">
+      <c r="G37" s="88"/>
+      <c r="H37" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J37" s="92" t="s">
+      <c r="I37" s="90" t="s">
         <v>133</v>
       </c>
-      <c r="K37" s="34">
+      <c r="J37" s="34">
         <v>46307</v>
       </c>
-      <c r="L37" s="35">
+      <c r="K37" s="35">
         <v>46307</v>
       </c>
-      <c r="M37" s="34"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P37" s="65">
-        <f t="shared" si="14"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O37" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="60">
+        <f>IF(N37=0,0,MAX(0,MIN(N37,$K$1-J37+1)))</f>
         <v>0</v>
       </c>
       <c r="Q37" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T37" s="68">
+      <c r="R37" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U37" s="69">
+      <c r="S37" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V37" s="177">
+      <c r="T37" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W37" s="171"/>
-      <c r="X37" s="156"/>
-      <c r="Y37" s="162"/>
-      <c r="Z37" s="175"/>
-      <c r="AA37" s="156"/>
-      <c r="AB37" s="176"/>
-      <c r="AC37" s="168" t="s">
+      <c r="U37" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="144"/>
+      <c r="W37" s="129"/>
+      <c r="X37" s="135"/>
+      <c r="Y37" s="148"/>
+      <c r="Z37" s="129"/>
+      <c r="AA37" s="149"/>
+      <c r="AB37" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD37" s="156"/>
-      <c r="AE37" s="176"/>
+      <c r="AC37" s="129"/>
+      <c r="AD37" s="149"/>
     </row>
-    <row r="38" spans="1:31" ht="30" customHeight="1">
+    <row r="38" spans="1:30" ht="30" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="30"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="136" t="s">
+      <c r="C38" s="81"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="112" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="144" t="s">
+      <c r="F38" s="120" t="s">
         <v>144</v>
       </c>
-      <c r="G38" s="124"/>
-      <c r="H38" s="90"/>
-      <c r="I38" s="64" t="s">
+      <c r="G38" s="88"/>
+      <c r="H38" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J38" s="92" t="s">
+      <c r="I38" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="K38" s="34">
+      <c r="J38" s="34">
         <v>46307</v>
       </c>
-      <c r="L38" s="35">
+      <c r="K38" s="35">
         <v>46307</v>
       </c>
-      <c r="M38" s="34"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P38" s="65">
-        <f t="shared" si="14"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O38" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="60">
+        <f>IF(N38=0,0,MAX(0,MIN(N38,$K$1-J38+1)))</f>
         <v>0</v>
       </c>
       <c r="Q38" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R38" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T38" s="68">
+      <c r="R38" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U38" s="69">
+      <c r="S38" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V38" s="177">
+      <c r="T38" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W38" s="171"/>
-      <c r="X38" s="156"/>
-      <c r="Y38" s="162"/>
-      <c r="Z38" s="175"/>
-      <c r="AA38" s="156"/>
-      <c r="AB38" s="176"/>
-      <c r="AC38" s="168" t="s">
+      <c r="U38" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="144"/>
+      <c r="W38" s="129"/>
+      <c r="X38" s="135"/>
+      <c r="Y38" s="148"/>
+      <c r="Z38" s="129"/>
+      <c r="AA38" s="149"/>
+      <c r="AB38" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD38" s="156"/>
-      <c r="AE38" s="176"/>
+      <c r="AC38" s="129"/>
+      <c r="AD38" s="149"/>
     </row>
-    <row r="39" spans="1:31" ht="30" customHeight="1">
+    <row r="39" spans="1:30" ht="30" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="30"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="134"/>
-      <c r="E39" s="136" t="s">
+      <c r="C39" s="81"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="112" t="s">
         <v>112</v>
       </c>
-      <c r="F39" s="144" t="s">
+      <c r="F39" s="120" t="s">
         <v>145</v>
       </c>
-      <c r="G39" s="124"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="64" t="s">
+      <c r="G39" s="88"/>
+      <c r="H39" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J39" s="92" t="s">
+      <c r="I39" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="K39" s="34">
+      <c r="J39" s="34">
         <v>46307</v>
       </c>
-      <c r="L39" s="35">
+      <c r="K39" s="35">
         <v>46307</v>
       </c>
-      <c r="M39" s="34"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P39" s="65">
-        <f t="shared" si="14"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O39" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="60">
+        <f>IF(N39=0,0,MAX(0,MIN(N39,$K$1-J39+1)))</f>
         <v>0</v>
       </c>
       <c r="Q39" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R39" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T39" s="68">
+      <c r="R39" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U39" s="69">
+      <c r="S39" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V39" s="177">
+      <c r="T39" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W39" s="171"/>
-      <c r="X39" s="156"/>
-      <c r="Y39" s="162"/>
-      <c r="Z39" s="175"/>
-      <c r="AA39" s="156"/>
-      <c r="AB39" s="176"/>
-      <c r="AC39" s="168" t="s">
+      <c r="U39" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V39" s="144"/>
+      <c r="W39" s="129"/>
+      <c r="X39" s="135"/>
+      <c r="Y39" s="148"/>
+      <c r="Z39" s="129"/>
+      <c r="AA39" s="149"/>
+      <c r="AB39" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD39" s="156"/>
-      <c r="AE39" s="176"/>
+      <c r="AC39" s="129"/>
+      <c r="AD39" s="149"/>
     </row>
-    <row r="40" spans="1:31" ht="30" customHeight="1">
+    <row r="40" spans="1:30" ht="30" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="30"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="136" t="s">
+      <c r="C40" s="81"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="F40" s="144" t="s">
+      <c r="F40" s="120" t="s">
         <v>146</v>
       </c>
-      <c r="G40" s="124"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="64" t="s">
+      <c r="G40" s="88"/>
+      <c r="H40" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J40" s="92" t="s">
+      <c r="I40" s="90" t="s">
         <v>136</v>
       </c>
-      <c r="K40" s="34">
+      <c r="J40" s="34">
         <v>46307</v>
       </c>
-      <c r="L40" s="35">
+      <c r="K40" s="35">
         <v>46307</v>
       </c>
-      <c r="M40" s="34"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P40" s="65">
-        <f t="shared" si="14"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O40" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="60">
+        <f>IF(N40=0,0,MAX(0,MIN(N40,$K$1-J40+1)))</f>
         <v>0</v>
       </c>
       <c r="Q40" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R40" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T40" s="68">
+      <c r="R40" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U40" s="69">
+      <c r="S40" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V40" s="177">
+      <c r="T40" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W40" s="171"/>
-      <c r="X40" s="156"/>
-      <c r="Y40" s="162"/>
-      <c r="Z40" s="175"/>
-      <c r="AA40" s="156"/>
-      <c r="AB40" s="176"/>
-      <c r="AC40" s="168" t="s">
+      <c r="U40" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="144"/>
+      <c r="W40" s="129"/>
+      <c r="X40" s="135"/>
+      <c r="Y40" s="148"/>
+      <c r="Z40" s="129"/>
+      <c r="AA40" s="149"/>
+      <c r="AB40" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD40" s="156"/>
-      <c r="AE40" s="176"/>
+      <c r="AC40" s="129"/>
+      <c r="AD40" s="149"/>
     </row>
-    <row r="41" spans="1:31" ht="30" customHeight="1">
+    <row r="41" spans="1:30" ht="30" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="30"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="134"/>
-      <c r="E41" s="136" t="s">
+      <c r="C41" s="81"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="112" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="144" t="s">
+      <c r="F41" s="120" t="s">
         <v>147</v>
       </c>
-      <c r="G41" s="124"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="64" t="s">
+      <c r="G41" s="88"/>
+      <c r="H41" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J41" s="92" t="s">
+      <c r="I41" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="K41" s="34">
+      <c r="J41" s="34">
         <v>46307</v>
       </c>
-      <c r="L41" s="35">
+      <c r="K41" s="35">
         <v>46307</v>
       </c>
-      <c r="M41" s="34"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P41" s="65">
-        <f t="shared" si="14"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O41" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="60">
+        <f>IF(N41=0,0,MAX(0,MIN(N41,$K$1-J41+1)))</f>
         <v>0</v>
       </c>
       <c r="Q41" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R41" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T41" s="68">
+      <c r="R41" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U41" s="69">
+      <c r="S41" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V41" s="177">
+      <c r="T41" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W41" s="171"/>
-      <c r="X41" s="156"/>
-      <c r="Y41" s="162"/>
-      <c r="Z41" s="175"/>
-      <c r="AA41" s="156"/>
-      <c r="AB41" s="176"/>
-      <c r="AC41" s="168" t="s">
+      <c r="U41" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="144"/>
+      <c r="W41" s="129"/>
+      <c r="X41" s="135"/>
+      <c r="Y41" s="148"/>
+      <c r="Z41" s="129"/>
+      <c r="AA41" s="149"/>
+      <c r="AB41" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD41" s="156"/>
-      <c r="AE41" s="176"/>
+      <c r="AC41" s="129"/>
+      <c r="AD41" s="149"/>
     </row>
-    <row r="42" spans="1:31" ht="30" customHeight="1">
+    <row r="42" spans="1:30" ht="30" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="30"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="134"/>
-      <c r="E42" s="136" t="s">
+      <c r="C42" s="81"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="144" t="s">
+      <c r="F42" s="120" t="s">
         <v>148</v>
       </c>
-      <c r="G42" s="124"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="64" t="s">
+      <c r="G42" s="88"/>
+      <c r="H42" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J42" s="92" t="s">
+      <c r="I42" s="90" t="s">
         <v>138</v>
       </c>
-      <c r="K42" s="34">
+      <c r="J42" s="34">
         <v>46307</v>
       </c>
-      <c r="L42" s="35">
+      <c r="K42" s="35">
         <v>46307</v>
       </c>
-      <c r="M42" s="34"/>
-      <c r="N42" s="35"/>
-      <c r="O42" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P42" s="65">
-        <f t="shared" si="14"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="35"/>
+      <c r="N42" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O42" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="60">
+        <f>IF(N42=0,0,MAX(0,MIN(N42,$K$1-J42+1)))</f>
         <v>0</v>
       </c>
       <c r="Q42" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R42" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T42" s="68">
+      <c r="R42" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U42" s="69">
+      <c r="S42" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V42" s="177">
+      <c r="T42" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W42" s="171"/>
-      <c r="X42" s="156"/>
-      <c r="Y42" s="162"/>
-      <c r="Z42" s="175"/>
-      <c r="AA42" s="156"/>
-      <c r="AB42" s="176"/>
-      <c r="AC42" s="168" t="s">
+      <c r="U42" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="144"/>
+      <c r="W42" s="129"/>
+      <c r="X42" s="135"/>
+      <c r="Y42" s="148"/>
+      <c r="Z42" s="129"/>
+      <c r="AA42" s="149"/>
+      <c r="AB42" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD42" s="156"/>
-      <c r="AE42" s="176"/>
+      <c r="AC42" s="129"/>
+      <c r="AD42" s="149"/>
     </row>
-    <row r="43" spans="1:31" ht="30" customHeight="1">
+    <row r="43" spans="1:30" ht="30" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="30"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="134"/>
-      <c r="E43" s="136" t="s">
+      <c r="C43" s="81"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="144" t="s">
+      <c r="F43" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="G43" s="124"/>
-      <c r="H43" s="90"/>
-      <c r="I43" s="64" t="s">
+      <c r="G43" s="88"/>
+      <c r="H43" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J43" s="92" t="s">
+      <c r="I43" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="K43" s="34">
+      <c r="J43" s="34">
         <v>46307</v>
       </c>
-      <c r="L43" s="35">
+      <c r="K43" s="35">
         <v>46307</v>
       </c>
-      <c r="M43" s="34"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P43" s="65">
-        <f t="shared" si="14"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O43" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="60">
+        <f>IF(N43=0,0,MAX(0,MIN(N43,$K$1-J43+1)))</f>
         <v>0</v>
       </c>
       <c r="Q43" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R43" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T43" s="68">
+      <c r="R43" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U43" s="69">
+      <c r="S43" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V43" s="177">
+      <c r="T43" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W43" s="171"/>
-      <c r="X43" s="156"/>
-      <c r="Y43" s="162"/>
-      <c r="Z43" s="175"/>
-      <c r="AA43" s="156"/>
-      <c r="AB43" s="176"/>
-      <c r="AC43" s="168" t="s">
+      <c r="U43" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="144"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="135"/>
+      <c r="Y43" s="148"/>
+      <c r="Z43" s="129"/>
+      <c r="AA43" s="149"/>
+      <c r="AB43" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD43" s="156"/>
-      <c r="AE43" s="176"/>
+      <c r="AC43" s="129"/>
+      <c r="AD43" s="149"/>
     </row>
-    <row r="44" spans="1:31" ht="30" customHeight="1">
+    <row r="44" spans="1:30" ht="30" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="30"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="134"/>
-      <c r="E44" s="136" t="s">
+      <c r="C44" s="81"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="F44" s="144" t="s">
+      <c r="F44" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="G44" s="124"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="64" t="s">
+      <c r="G44" s="88"/>
+      <c r="H44" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J44" s="92" t="s">
+      <c r="I44" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="K44" s="34">
+      <c r="J44" s="34">
         <v>46307</v>
       </c>
-      <c r="L44" s="35">
+      <c r="K44" s="35">
         <v>46307</v>
       </c>
-      <c r="M44" s="34"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P44" s="65">
-        <f t="shared" si="14"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O44" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="60">
+        <f>IF(N44=0,0,MAX(0,MIN(N44,$K$1-J44+1)))</f>
         <v>0</v>
       </c>
       <c r="Q44" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R44" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T44" s="68">
+      <c r="R44" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U44" s="69">
+      <c r="S44" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V44" s="177">
+      <c r="T44" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W44" s="171"/>
-      <c r="X44" s="156"/>
-      <c r="Y44" s="162"/>
-      <c r="Z44" s="175"/>
-      <c r="AA44" s="156"/>
-      <c r="AB44" s="176"/>
-      <c r="AC44" s="168" t="s">
+      <c r="U44" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="144"/>
+      <c r="W44" s="129"/>
+      <c r="X44" s="135"/>
+      <c r="Y44" s="148"/>
+      <c r="Z44" s="129"/>
+      <c r="AA44" s="149"/>
+      <c r="AB44" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="AD44" s="156"/>
-      <c r="AE44" s="172"/>
+      <c r="AC44" s="129"/>
+      <c r="AD44" s="145"/>
     </row>
-    <row r="45" spans="1:31" ht="30" customHeight="1">
+    <row r="45" spans="1:30" ht="30" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="30"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="134"/>
-      <c r="E45" s="136" t="s">
+      <c r="C45" s="81"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="112" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="144" t="s">
+      <c r="F45" s="120" t="s">
         <v>151</v>
       </c>
-      <c r="G45" s="124"/>
-      <c r="H45" s="90"/>
-      <c r="I45" s="64" t="s">
+      <c r="G45" s="88"/>
+      <c r="H45" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J45" s="92" t="s">
+      <c r="I45" s="90" t="s">
         <v>141</v>
       </c>
-      <c r="K45" s="34">
+      <c r="J45" s="34">
         <v>46307</v>
       </c>
-      <c r="L45" s="35">
+      <c r="K45" s="35">
         <v>46307</v>
       </c>
-      <c r="M45" s="34"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="64">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P45" s="65">
-        <f t="shared" si="14"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O45" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="60">
+        <f>IF(N45=0,0,MAX(0,MIN(N45,$K$1-J45+1)))</f>
         <v>0</v>
       </c>
       <c r="Q45" s="64">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R45" s="66">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="67">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="T45" s="68">
+      <c r="R45" s="65">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="U45" s="69">
+      <c r="S45" s="66">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="V45" s="177">
+      <c r="T45" s="67">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="W45" s="171"/>
-      <c r="X45" s="156"/>
-      <c r="Y45" s="162"/>
-      <c r="Z45" s="175"/>
-      <c r="AA45" s="156"/>
-      <c r="AB45" s="176"/>
-      <c r="AC45" s="168" t="s">
+      <c r="U45" s="150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V45" s="144"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="135"/>
+      <c r="Y45" s="148"/>
+      <c r="Z45" s="129"/>
+      <c r="AA45" s="149"/>
+      <c r="AB45" s="141" t="s">
         <v>154</v>
       </c>
-      <c r="AD45" s="156"/>
-      <c r="AE45" s="172"/>
+      <c r="AC45" s="129"/>
+      <c r="AD45" s="145"/>
     </row>
-    <row r="46" spans="1:31" ht="30" customHeight="1">
+    <row r="46" spans="1:30" ht="30" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="30"/>
-      <c r="C46" s="83"/>
-      <c r="D46" s="134"/>
-      <c r="E46" s="136" t="s">
+      <c r="C46" s="81"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="112" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="144" t="s">
+      <c r="F46" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="G46" s="124"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="64" t="s">
+      <c r="G46" s="74"/>
+      <c r="H46" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="J46" s="88" t="s">
+      <c r="I46" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="K46" s="34">
+      <c r="J46" s="34">
         <v>46307</v>
       </c>
-      <c r="L46" s="35">
+      <c r="K46" s="35">
         <v>46307</v>
       </c>
-      <c r="M46" s="36"/>
-      <c r="N46" s="37"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="74">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="O46" s="76">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="P46" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="76">
+      <c r="P46" s="74">
+        <f>IF(N46=0,0,MAX(0,MIN(N46,$K$1-J46+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R46" s="80">
+      <c r="R46" s="125">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S46" s="150">
+      <c r="S46" s="126">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T46" s="151">
+      <c r="T46" s="127">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U46" s="152">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V46" s="178">
+      <c r="U46" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W46" s="195"/>
-      <c r="X46" s="196"/>
-      <c r="Y46" s="194"/>
-      <c r="Z46" s="203"/>
-      <c r="AA46" s="204"/>
-      <c r="AB46" s="205"/>
-      <c r="AC46" s="206" t="s">
+      <c r="V46" s="164"/>
+      <c r="W46" s="165"/>
+      <c r="X46" s="163"/>
+      <c r="Y46" s="170"/>
+      <c r="Z46" s="171"/>
+      <c r="AA46" s="172"/>
+      <c r="AB46" s="173" t="s">
         <v>154</v>
       </c>
-      <c r="AD46" s="204"/>
-      <c r="AE46" s="197"/>
+      <c r="AC46" s="171"/>
+      <c r="AD46" s="166"/>
     </row>
-    <row r="47" spans="1:31" ht="30" customHeight="1">
+    <row r="47" spans="1:30" ht="30" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="30">
         <v>4</v>
       </c>
-      <c r="C47" s="81">
+      <c r="C47" s="79">
         <v>0.15</v>
       </c>
-      <c r="D47" s="97" t="s">
+      <c r="D47" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="E47" s="136" t="s">
+      <c r="E47" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="F47" s="145" t="s">
+      <c r="F47" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="G47" s="146"/>
-      <c r="H47" s="61" t="s">
+      <c r="G47" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="62"/>
-      <c r="J47" s="82" t="s">
+      <c r="H47" s="60"/>
+      <c r="I47" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="K47" s="34">
+      <c r="J47" s="34">
         <v>46303</v>
       </c>
-      <c r="L47" s="35">
+      <c r="K47" s="35">
         <v>46303</v>
       </c>
-      <c r="M47" s="34"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="62">
+      <c r="L47" s="34"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="60">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P47" s="65">
+      <c r="O47" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="62">
+      <c r="P47" s="60">
+        <f>IF(N47=0,0,MAX(0,MIN(N47,$K$1-J47+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R47" s="66">
+      <c r="R47" s="122">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S47" s="147">
+      <c r="S47" s="123">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T47" s="148">
+      <c r="T47" s="124">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U47" s="149">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V47" s="179">
+      <c r="U47" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W47" s="188"/>
-      <c r="X47" s="189"/>
-      <c r="Y47" s="199" t="s">
+      <c r="V47" s="159"/>
+      <c r="W47" s="160"/>
+      <c r="X47" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="Z47" s="188"/>
-      <c r="AA47" s="189"/>
-      <c r="AB47" s="190"/>
-      <c r="AC47" s="191"/>
-      <c r="AD47" s="189"/>
-      <c r="AE47" s="190"/>
+      <c r="Y47" s="159"/>
+      <c r="Z47" s="160"/>
+      <c r="AA47" s="161"/>
+      <c r="AB47" s="162"/>
+      <c r="AC47" s="160"/>
+      <c r="AD47" s="161"/>
     </row>
-    <row r="48" spans="1:31" ht="30" customHeight="1">
+    <row r="48" spans="1:30" ht="30" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="30"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="136" t="s">
+      <c r="C48" s="81"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="F48" s="144" t="s">
+      <c r="F48" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="G48" s="124"/>
-      <c r="H48" s="61" t="s">
+      <c r="G48" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I48" s="62"/>
-      <c r="J48" s="82" t="s">
+      <c r="H48" s="60"/>
+      <c r="I48" s="80" t="s">
         <v>67</v>
+      </c>
+      <c r="J48" s="34">
+        <v>46307</v>
       </c>
       <c r="K48" s="34">
         <v>46307</v>
       </c>
-      <c r="L48" s="34">
-        <v>46307</v>
-      </c>
-      <c r="M48" s="34"/>
-      <c r="N48" s="35"/>
-      <c r="O48" s="64">
+      <c r="L48" s="34"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P48" s="65">
+      <c r="O48" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="60">
+        <f>IF(N48=0,0,MAX(0,MIN(N48,$K$1-J48+1)))</f>
         <v>0</v>
       </c>
       <c r="Q48" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R48" s="66">
+      <c r="R48" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S48" s="67">
+      <c r="S48" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T48" s="68">
+      <c r="T48" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U48" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V48" s="177">
+      <c r="U48" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W48" s="171"/>
-      <c r="X48" s="156"/>
-      <c r="Y48" s="162"/>
-      <c r="Z48" s="171"/>
-      <c r="AA48" s="159"/>
-      <c r="AB48" s="172"/>
-      <c r="AC48" s="168" t="s">
+      <c r="V48" s="144"/>
+      <c r="W48" s="129"/>
+      <c r="X48" s="135"/>
+      <c r="Y48" s="144"/>
+      <c r="Z48" s="132"/>
+      <c r="AA48" s="145"/>
+      <c r="AB48" s="141" t="s">
         <v>154</v>
       </c>
-      <c r="AD48" s="159"/>
-      <c r="AE48" s="176"/>
+      <c r="AC48" s="132"/>
+      <c r="AD48" s="149"/>
     </row>
-    <row r="49" spans="1:31" ht="30" customHeight="1">
+    <row r="49" spans="1:30" ht="30" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="30"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="136" t="s">
+      <c r="C49" s="81"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="F49" s="144" t="s">
+      <c r="F49" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="G49" s="124"/>
-      <c r="H49" s="98" t="s">
+      <c r="G49" s="96" t="s">
         <v>82</v>
       </c>
-      <c r="I49" s="99"/>
-      <c r="J49" s="100" t="s">
+      <c r="H49" s="97"/>
+      <c r="I49" s="98" t="s">
         <v>70</v>
+      </c>
+      <c r="J49" s="34">
+        <v>46307</v>
       </c>
       <c r="K49" s="34">
         <v>46307</v>
       </c>
-      <c r="L49" s="34">
-        <v>46307</v>
-      </c>
-      <c r="M49" s="34"/>
-      <c r="N49" s="35"/>
-      <c r="O49" s="101">
+      <c r="L49" s="34"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P49" s="65">
+      <c r="O49" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="101">
+      <c r="P49" s="60">
+        <f>IF(N49=0,0,MAX(0,MIN(N49,$K$1-J49+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R49" s="66">
+      <c r="R49" s="99">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S49" s="102">
+      <c r="S49" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T49" s="68">
+      <c r="T49" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U49" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V49" s="177">
+      <c r="U49" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W49" s="171"/>
-      <c r="X49" s="160"/>
-      <c r="Y49" s="165"/>
-      <c r="Z49" s="173"/>
-      <c r="AA49" s="160"/>
-      <c r="AB49" s="174"/>
-      <c r="AC49" s="168" t="s">
+      <c r="V49" s="144"/>
+      <c r="W49" s="133"/>
+      <c r="X49" s="138"/>
+      <c r="Y49" s="146"/>
+      <c r="Z49" s="133"/>
+      <c r="AA49" s="147"/>
+      <c r="AB49" s="141" t="s">
         <v>154</v>
       </c>
-      <c r="AD49" s="160"/>
-      <c r="AE49" s="184"/>
+      <c r="AC49" s="133"/>
+      <c r="AD49" s="156"/>
     </row>
-    <row r="50" spans="1:31" ht="30" customHeight="1">
+    <row r="50" spans="1:30" ht="30" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="30"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="60"/>
-      <c r="E50" s="136" t="s">
+      <c r="C50" s="81"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="112" t="s">
         <v>78</v>
       </c>
-      <c r="F50" s="144" t="s">
+      <c r="F50" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="G50" s="124"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="99" t="s">
+      <c r="G50" s="100"/>
+      <c r="H50" s="97" t="s">
         <v>83</v>
       </c>
-      <c r="J50" s="100" t="s">
+      <c r="I50" s="98" t="s">
         <v>80</v>
+      </c>
+      <c r="J50" s="34">
+        <v>46308</v>
       </c>
       <c r="K50" s="34">
         <v>46308</v>
       </c>
-      <c r="L50" s="34">
-        <v>46308</v>
-      </c>
-      <c r="M50" s="34"/>
-      <c r="N50" s="35"/>
-      <c r="O50" s="101">
+      <c r="L50" s="34"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P50" s="65">
+      <c r="O50" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="101">
+      <c r="P50" s="60">
+        <f>IF(N50=0,0,MAX(0,MIN(N50,$K$1-J50+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R50" s="66">
+      <c r="R50" s="99">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S50" s="102">
+      <c r="S50" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T50" s="68">
+      <c r="T50" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U50" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V50" s="177">
+      <c r="U50" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W50" s="171"/>
-      <c r="X50" s="156"/>
-      <c r="Y50" s="162"/>
-      <c r="Z50" s="171"/>
-      <c r="AA50" s="156"/>
-      <c r="AB50" s="172"/>
-      <c r="AC50" s="158"/>
-      <c r="AD50" s="159" t="s">
+      <c r="V50" s="144"/>
+      <c r="W50" s="129"/>
+      <c r="X50" s="135"/>
+      <c r="Y50" s="144"/>
+      <c r="Z50" s="129"/>
+      <c r="AA50" s="145"/>
+      <c r="AB50" s="131"/>
+      <c r="AC50" s="132" t="s">
         <v>154</v>
       </c>
-      <c r="AE50" s="176"/>
+      <c r="AD50" s="149"/>
     </row>
-    <row r="51" spans="1:31" ht="30" customHeight="1">
+    <row r="51" spans="1:30" ht="30" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="33"/>
-      <c r="C51" s="86"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="136"/>
-      <c r="F51" s="143"/>
-      <c r="G51" s="126"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="76"/>
-      <c r="J51" s="88"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="40"/>
-      <c r="N51" s="40"/>
+      <c r="C51" s="84"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="86"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="38"/>
+      <c r="M51" s="38"/>
+      <c r="N51" s="74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="O51" s="76">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="78">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q51" s="76">
+      <c r="P51" s="74">
+        <f>IF(N51=0,0,MAX(0,MIN(N51,$K$1-J51+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="78">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R51" s="80">
+      <c r="R51" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S51" s="67">
+      <c r="S51" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T51" s="68">
+      <c r="T51" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U51" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V51" s="177">
+      <c r="U51" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W51" s="171"/>
-      <c r="X51" s="156"/>
-      <c r="Y51" s="162"/>
-      <c r="Z51" s="171"/>
-      <c r="AA51" s="156"/>
-      <c r="AB51" s="172"/>
-      <c r="AC51" s="158"/>
-      <c r="AD51" s="156"/>
-      <c r="AE51" s="176"/>
+      <c r="V51" s="144"/>
+      <c r="W51" s="129"/>
+      <c r="X51" s="135"/>
+      <c r="Y51" s="144"/>
+      <c r="Z51" s="129"/>
+      <c r="AA51" s="145"/>
+      <c r="AB51" s="131"/>
+      <c r="AC51" s="129"/>
+      <c r="AD51" s="149"/>
     </row>
-    <row r="52" spans="1:31" ht="30" customHeight="1">
+    <row r="52" spans="1:30" ht="30" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="30">
         <v>5</v>
       </c>
-      <c r="C52" s="81">
+      <c r="C52" s="79">
         <v>0.15</v>
       </c>
-      <c r="D52" s="60" t="s">
+      <c r="D52" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="136" t="s">
+      <c r="E52" s="112" t="s">
         <v>81</v>
       </c>
-      <c r="F52" s="145" t="s">
+      <c r="F52" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="146"/>
-      <c r="H52" s="61" t="s">
+      <c r="G52" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="I52" s="62" t="s">
+      <c r="H52" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="J52" s="85" t="s">
+      <c r="I52" s="83" t="s">
         <v>72</v>
+      </c>
+      <c r="J52" s="34">
+        <v>46309</v>
       </c>
       <c r="K52" s="34">
         <v>46309</v>
       </c>
-      <c r="L52" s="34">
-        <v>46309</v>
-      </c>
+      <c r="L52" s="34"/>
       <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="62"/>
-      <c r="P52" s="65">
+      <c r="N52" s="60">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O52" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="62">
+      <c r="P52" s="60">
+        <f>IF(N52=0,0,MAX(0,MIN(N52,$K$1-J52+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R52" s="66">
+      <c r="R52" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S52" s="67">
+      <c r="S52" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T52" s="68">
+      <c r="T52" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U52" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V52" s="177">
+      <c r="U52" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W52" s="171"/>
-      <c r="X52" s="156"/>
-      <c r="Y52" s="162"/>
-      <c r="Z52" s="171"/>
-      <c r="AA52" s="156"/>
-      <c r="AB52" s="172"/>
-      <c r="AC52" s="158"/>
-      <c r="AD52" s="156"/>
-      <c r="AE52" s="176" t="s">
+      <c r="V52" s="144"/>
+      <c r="W52" s="129"/>
+      <c r="X52" s="135"/>
+      <c r="Y52" s="144"/>
+      <c r="Z52" s="129"/>
+      <c r="AA52" s="145"/>
+      <c r="AB52" s="131"/>
+      <c r="AC52" s="129"/>
+      <c r="AD52" s="149" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="30" customHeight="1">
+    <row r="53" spans="1:30" ht="30" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="30"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="136" t="s">
+      <c r="C53" s="81"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="F53" s="124" t="s">
+      <c r="F53" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="G53" s="125"/>
-      <c r="H53" s="84" t="s">
+      <c r="G53" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="64" t="s">
+      <c r="H53" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="85" t="s">
+      <c r="I53" s="83" t="s">
         <v>75</v>
+      </c>
+      <c r="J53" s="34">
+        <v>46309</v>
       </c>
       <c r="K53" s="34">
         <v>46309</v>
       </c>
-      <c r="L53" s="34">
-        <v>46309</v>
-      </c>
-      <c r="M53" s="72"/>
-      <c r="N53" s="72"/>
-      <c r="O53" s="64">
+      <c r="L53" s="70"/>
+      <c r="M53" s="70"/>
+      <c r="N53" s="62">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P53" s="65">
+      <c r="O53" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="60">
+        <f>IF(N53=0,0,MAX(0,MIN(N53,$K$1-J53+1)))</f>
         <v>0</v>
       </c>
       <c r="Q53" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R53" s="66">
+      <c r="R53" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S53" s="67">
+      <c r="S53" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T53" s="68">
+      <c r="T53" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U53" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="177">
+      <c r="U53" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W53" s="171"/>
-      <c r="X53" s="156"/>
-      <c r="Y53" s="162"/>
-      <c r="Z53" s="171"/>
-      <c r="AA53" s="156"/>
-      <c r="AB53" s="172"/>
-      <c r="AC53" s="158"/>
-      <c r="AD53" s="156"/>
-      <c r="AE53" s="176" t="s">
+      <c r="V53" s="144"/>
+      <c r="W53" s="129"/>
+      <c r="X53" s="135"/>
+      <c r="Y53" s="144"/>
+      <c r="Z53" s="129"/>
+      <c r="AA53" s="145"/>
+      <c r="AB53" s="131"/>
+      <c r="AC53" s="129"/>
+      <c r="AD53" s="149" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="30" customHeight="1">
+    <row r="54" spans="1:30" ht="30" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="29"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="136"/>
-      <c r="F54" s="124"/>
-      <c r="G54" s="125"/>
-      <c r="H54" s="84"/>
-      <c r="I54" s="64"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="72"/>
-      <c r="L54" s="72"/>
-      <c r="M54" s="72"/>
-      <c r="N54" s="72"/>
-      <c r="O54" s="64">
+      <c r="C54" s="81"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="107"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="83"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="70"/>
+      <c r="M54" s="70"/>
+      <c r="N54" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P54" s="65">
+      <c r="O54" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="62">
+        <f>IF(N54=0,0,MAX(0,MIN(N54,$K$1-J54+1)))</f>
         <v>0</v>
       </c>
       <c r="Q54" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R54" s="66">
+      <c r="R54" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S54" s="67">
+      <c r="S54" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T54" s="68">
+      <c r="T54" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U54" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="177">
+      <c r="U54" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W54" s="171"/>
-      <c r="X54" s="156"/>
-      <c r="Y54" s="162"/>
-      <c r="Z54" s="171"/>
-      <c r="AA54" s="156"/>
-      <c r="AB54" s="172"/>
-      <c r="AC54" s="158"/>
-      <c r="AD54" s="156"/>
-      <c r="AE54" s="176" t="s">
+      <c r="V54" s="144"/>
+      <c r="W54" s="129"/>
+      <c r="X54" s="135"/>
+      <c r="Y54" s="144"/>
+      <c r="Z54" s="129"/>
+      <c r="AA54" s="145"/>
+      <c r="AB54" s="131"/>
+      <c r="AC54" s="129"/>
+      <c r="AD54" s="149" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="30" customHeight="1">
+    <row r="55" spans="1:30" ht="30" customHeight="1">
       <c r="A55" s="5"/>
       <c r="B55" s="29"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="136"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="125"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="64"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="72"/>
-      <c r="L55" s="72"/>
-      <c r="M55" s="72"/>
-      <c r="N55" s="72"/>
-      <c r="O55" s="64">
+      <c r="C55" s="81"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="107"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="83"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="70"/>
+      <c r="M55" s="70"/>
+      <c r="N55" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P55" s="65">
+      <c r="O55" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="62">
+        <f>IF(N55=0,0,MAX(0,MIN(N55,$K$1-J55+1)))</f>
         <v>0</v>
       </c>
       <c r="Q55" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R55" s="66">
+      <c r="R55" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S55" s="67">
+      <c r="S55" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T55" s="68">
+      <c r="T55" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U55" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V55" s="177">
+      <c r="U55" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W55" s="171"/>
-      <c r="X55" s="156"/>
-      <c r="Y55" s="162"/>
-      <c r="Z55" s="171"/>
-      <c r="AA55" s="156"/>
-      <c r="AB55" s="172"/>
-      <c r="AC55" s="158"/>
-      <c r="AD55" s="156"/>
-      <c r="AE55" s="176"/>
+      <c r="V55" s="144"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="135"/>
+      <c r="Y55" s="144"/>
+      <c r="Z55" s="129"/>
+      <c r="AA55" s="145"/>
+      <c r="AB55" s="131"/>
+      <c r="AC55" s="129"/>
+      <c r="AD55" s="149"/>
     </row>
-    <row r="56" spans="1:31" ht="30" customHeight="1">
+    <row r="56" spans="1:30" ht="30" customHeight="1">
       <c r="A56" s="2"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="74"/>
-      <c r="E56" s="136"/>
-      <c r="F56" s="124"/>
-      <c r="G56" s="125"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="105"/>
-      <c r="K56" s="106"/>
-      <c r="L56" s="106"/>
-      <c r="M56" s="106"/>
-      <c r="N56" s="106"/>
-      <c r="O56" s="64">
+      <c r="B56" s="40"/>
+      <c r="C56" s="84"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="87"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="102"/>
+      <c r="J56" s="103"/>
+      <c r="K56" s="103"/>
+      <c r="L56" s="103"/>
+      <c r="M56" s="103"/>
+      <c r="N56" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P56" s="65">
+      <c r="O56" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="62">
+        <f>IF(N56=0,0,MAX(0,MIN(N56,$K$1-J56+1)))</f>
         <v>0</v>
       </c>
       <c r="Q56" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R56" s="66">
+      <c r="R56" s="65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S56" s="67">
+      <c r="S56" s="66">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T56" s="68">
+      <c r="T56" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U56" s="69">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V56" s="177">
+      <c r="U56" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W56" s="207"/>
-      <c r="X56" s="208"/>
-      <c r="Y56" s="209"/>
-      <c r="Z56" s="207"/>
-      <c r="AA56" s="208"/>
-      <c r="AB56" s="210"/>
-      <c r="AC56" s="211"/>
-      <c r="AD56" s="208"/>
-      <c r="AE56" s="212"/>
+      <c r="V56" s="174"/>
+      <c r="W56" s="175"/>
+      <c r="X56" s="176"/>
+      <c r="Y56" s="174"/>
+      <c r="Z56" s="175"/>
+      <c r="AA56" s="177"/>
+      <c r="AB56" s="178"/>
+      <c r="AC56" s="175"/>
+      <c r="AD56" s="179"/>
     </row>
-    <row r="57" spans="1:31" ht="33" customHeight="1">
+    <row r="57" spans="1:30" ht="33" customHeight="1">
       <c r="A57" s="6"/>
-      <c r="B57" s="130"/>
-      <c r="C57" s="130"/>
-      <c r="D57" s="130"/>
-      <c r="E57" s="130"/>
-      <c r="F57" s="130"/>
-      <c r="G57" s="130"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-      <c r="J57" s="107"/>
-      <c r="K57" s="107"/>
-      <c r="L57" s="107"/>
-      <c r="M57" s="44"/>
-      <c r="N57" s="44"/>
-      <c r="O57" s="45">
+      <c r="B57" s="182"/>
+      <c r="C57" s="182"/>
+      <c r="D57" s="182"/>
+      <c r="E57" s="182"/>
+      <c r="F57" s="182"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="42"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="43">
+        <f>SUM(N6:N56)</f>
+        <v>42</v>
+      </c>
+      <c r="O57" s="44">
         <f>SUM(O6:O56)</f>
-        <v>37</v>
-      </c>
-      <c r="P57" s="46">
+        <v>7</v>
+      </c>
+      <c r="P57" s="42">
         <f>SUM(P6:P56)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q57" s="44">
         <f>SUM(Q6:Q56)</f>
-        <v>3</v>
-      </c>
-      <c r="R57" s="46">
-        <f>SUM(R6:R56)</f>
-        <v>3</v>
-      </c>
-      <c r="S57" s="47">
+        <v>7</v>
+      </c>
+      <c r="R57" s="45">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="S57" s="45">
         <f t="shared" si="6"/>
-        <v>8.1081081081081086E-2</v>
-      </c>
-      <c r="T57" s="47">
-        <f t="shared" si="7"/>
-        <v>8.1081081081081086E-2</v>
-      </c>
-      <c r="U57" s="48">
-        <f>U5</f>
-        <v>0.15</v>
-      </c>
-      <c r="V57" s="180">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="T57" s="46">
+        <f>T5</f>
+        <v>0.3</v>
+      </c>
+      <c r="U57" s="153">
         <f t="shared" si="1"/>
-        <v>6.8918918918918909E-2</v>
-      </c>
-      <c r="W57" s="213"/>
-      <c r="X57" s="214"/>
-      <c r="Y57" s="214"/>
-      <c r="Z57" s="214"/>
-      <c r="AA57" s="214"/>
-      <c r="AB57" s="214"/>
-      <c r="AC57" s="214"/>
-      <c r="AD57" s="214"/>
-      <c r="AE57" s="214"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V57" s="180"/>
+      <c r="W57" s="181"/>
+      <c r="X57" s="181"/>
+      <c r="Y57" s="181"/>
+      <c r="Z57" s="181"/>
+      <c r="AA57" s="181"/>
+      <c r="AB57" s="181"/>
+      <c r="AC57" s="181"/>
+      <c r="AD57" s="181"/>
     </row>
-    <row r="58" spans="1:31" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:31" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:31" ht="6" customHeight="1"/>
-    <row r="61" spans="1:31" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:31" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:31" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:30" ht="6" customHeight="1"/>
+    <row r="61" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:30" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:30" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -7625,89 +7593,48 @@
     <row r="1005" ht="15.75" customHeight="1"/>
     <row r="1006" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="W57:AE57"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="W4:AE4"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="O1:Q1"/>
+  <mergeCells count="23">
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="F3:G5"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="V4:AD4"/>
+    <mergeCell ref="V57:AD57"/>
+    <mergeCell ref="B57:F57"/>
   </mergeCells>
   <phoneticPr fontId="31" type="noConversion"/>
-  <conditionalFormatting sqref="O6:R56">
+  <conditionalFormatting sqref="N6:Q56">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V56">
+  <conditionalFormatting sqref="R6:U56">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF44F300"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6:U56">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="-100%"/>
@@ -7719,27 +7646,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W6:AE56">
+  <conditionalFormatting sqref="V6:AD56">
     <cfRule type="expression" dxfId="1" priority="6">
-      <formula>AND(W$5 &gt;= $M6, W$5 &lt;= $N6, W$5 &lt;=$L$1)</formula>
+      <formula>AND(V$5 &gt;= $L6, V$5 &lt;= $M6, V$5 &lt;=$K$1)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="7">
-      <formula>AND(W$5 &gt;= $K6, W$5 &lt;= $L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S6:V56">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF44F300"/>
-      </colorScale>
+      <formula>AND(V$5 &gt;= $J6, V$5 &lt;= $K6)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="J6:N11 K12:N56" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>OR(NOT(ISERROR(DATEVALUE(J6))), AND(ISNUMBER(J6), LEFT(CELL("format", J6))="D"))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="I6:M11 J12:M56" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(I6))), AND(ISNUMBER(I6), LEFT(CELL("format", I6))="D"))</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
